--- a/public/route-rationalization-kashmir/Kashmir_Route_Frequency_Plan_v3.3.7_RTO.xlsx
+++ b/public/route-rationalization-kashmir/Kashmir_Route_Frequency_Plan_v3.3.7_RTO.xlsx
@@ -883,7 +883,7 @@
     <row r="9">
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>Version: v3.3.7  |  Generated: 29 May 2026</t>
+          <t>Version: v3.3.7  |  Generated: 30 May 2026</t>
         </is>
       </c>
     </row>
@@ -45437,7 +45437,7 @@
       </c>
       <c r="C5" s="75" t="inlineStr">
         <is>
-          <t>29 May 2026</t>
+          <t>30 May 2026</t>
         </is>
       </c>
     </row>

--- a/public/route-rationalization-kashmir/Kashmir_Route_Frequency_Plan_v3.3.7_RTO.xlsx
+++ b/public/route-rationalization-kashmir/Kashmir_Route_Frequency_Plan_v3.3.7_RTO.xlsx
@@ -1544,7 +1544,7 @@
       </c>
       <c r="D2" s="30" t="inlineStr">
         <is>
-          <t>SOURA ↔ LD</t>
+          <t>Soura to LD</t>
         </is>
       </c>
       <c r="E2" s="29" t="inlineStr">
@@ -1654,7 +1654,7 @@
       </c>
       <c r="D3" s="37" t="inlineStr">
         <is>
-          <t>PARIMPORA ↔ HAZRATBAL</t>
+          <t>Parimpora to Hazratbal</t>
         </is>
       </c>
       <c r="E3" s="36" t="inlineStr">
@@ -1760,7 +1760,7 @@
       </c>
       <c r="D4" s="43" t="inlineStr">
         <is>
-          <t>LAWAYPORA ↔ JEHANGIR CHOWK</t>
+          <t>Lawaypora to Jehangir Chowk</t>
         </is>
       </c>
       <c r="E4" s="42" t="inlineStr">
@@ -1870,7 +1870,7 @@
       </c>
       <c r="D5" s="37" t="inlineStr">
         <is>
-          <t>LALBAZAR ↔ LD</t>
+          <t>Lalbazar to LD</t>
         </is>
       </c>
       <c r="E5" s="36" t="inlineStr">
@@ -1976,7 +1976,7 @@
       </c>
       <c r="D6" s="47" t="inlineStr">
         <is>
-          <t>SOURA ↔ GADOORA</t>
+          <t>Soura to Gadoora</t>
         </is>
       </c>
       <c r="E6" s="46" t="inlineStr">
@@ -2082,7 +2082,7 @@
       </c>
       <c r="D7" s="37" t="inlineStr">
         <is>
-          <t>SOURA ↔ GANDERBAL</t>
+          <t>Soura to Ganderbal</t>
         </is>
       </c>
       <c r="E7" s="36" t="inlineStr">
@@ -2188,7 +2188,7 @@
       </c>
       <c r="D8" s="47" t="inlineStr">
         <is>
-          <t>SOURA ↔ GANDERBAL</t>
+          <t>Soura to Ganderbal</t>
         </is>
       </c>
       <c r="E8" s="46" t="inlineStr">
@@ -2294,7 +2294,7 @@
       </c>
       <c r="D9" s="37" t="inlineStr">
         <is>
-          <t>LALBAZAR ↔ LALCHOWK</t>
+          <t>Lalbazar to Lalchowk</t>
         </is>
       </c>
       <c r="E9" s="36" t="inlineStr">
@@ -2400,7 +2400,7 @@
       </c>
       <c r="D10" s="47" t="inlineStr">
         <is>
-          <t>JEHANGIR CHOWK ↔ SOURA</t>
+          <t>Jehangir Chowk to Soura</t>
         </is>
       </c>
       <c r="E10" s="46" t="inlineStr">
@@ -2506,7 +2506,7 @@
       </c>
       <c r="D11" s="30" t="inlineStr">
         <is>
-          <t>SOURA ↔ LD</t>
+          <t>Soura to LD</t>
         </is>
       </c>
       <c r="E11" s="29" t="inlineStr">
@@ -2616,7 +2616,7 @@
       </c>
       <c r="D12" s="30" t="inlineStr">
         <is>
-          <t>SOURA ↔ LD</t>
+          <t>Soura to LD</t>
         </is>
       </c>
       <c r="E12" s="29" t="inlineStr">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="D13" s="37" t="inlineStr">
         <is>
-          <t>SOURA ↔ HAZRATBAL</t>
+          <t>Soura to Hazratbal</t>
         </is>
       </c>
       <c r="E13" s="36" t="inlineStr">
@@ -2832,7 +2832,7 @@
       </c>
       <c r="D14" s="47" t="inlineStr">
         <is>
-          <t>TRC ↔ HAZRATBAL</t>
+          <t>TRC to Hazratbal</t>
         </is>
       </c>
       <c r="E14" s="46" t="inlineStr">
@@ -2938,7 +2938,7 @@
       </c>
       <c r="D15" s="30" t="inlineStr">
         <is>
-          <t>HAZRATBAL ↔ LD</t>
+          <t>Hazratbal to LD</t>
         </is>
       </c>
       <c r="E15" s="29" t="inlineStr">
@@ -3048,7 +3048,7 @@
       </c>
       <c r="D16" s="47" t="inlineStr">
         <is>
-          <t>SOURA ↔ RAILWAY STATION</t>
+          <t>Soura to Railway Station</t>
         </is>
       </c>
       <c r="E16" s="46" t="inlineStr">
@@ -3154,7 +3154,7 @@
       </c>
       <c r="D17" s="30" t="inlineStr">
         <is>
-          <t>SOURA ↔ LD</t>
+          <t>Soura to LD</t>
         </is>
       </c>
       <c r="E17" s="29" t="inlineStr">
@@ -3264,7 +3264,7 @@
       </c>
       <c r="D18" s="47" t="inlineStr">
         <is>
-          <t>MALBAGH ↔ LD</t>
+          <t>Malbagh to LD</t>
         </is>
       </c>
       <c r="E18" s="46" t="inlineStr">
@@ -3370,7 +3370,7 @@
       </c>
       <c r="D19" s="52" t="inlineStr">
         <is>
-          <t>JEHANGIR CHOWK ↔ JVC</t>
+          <t>Jehangir Chowk to JVC</t>
         </is>
       </c>
       <c r="E19" s="51" t="inlineStr">
@@ -3476,7 +3476,7 @@
       </c>
       <c r="D20" s="56" t="inlineStr">
         <is>
-          <t>JEHANGIR CHOWK ↔ JVC</t>
+          <t>Jehangir Chowk to JVC</t>
         </is>
       </c>
       <c r="E20" s="55" t="inlineStr">
@@ -3582,7 +3582,7 @@
       </c>
       <c r="D21" s="30" t="inlineStr">
         <is>
-          <t>SOURA ↔ PARIMPORA</t>
+          <t>Soura to Parimpora</t>
         </is>
       </c>
       <c r="E21" s="29" t="inlineStr">
@@ -3692,7 +3692,7 @@
       </c>
       <c r="D22" s="30" t="inlineStr">
         <is>
-          <t>SOURA ↔ HAZRATBAL</t>
+          <t>Soura to Hazratbal</t>
         </is>
       </c>
       <c r="E22" s="29" t="inlineStr">
@@ -3802,7 +3802,7 @@
       </c>
       <c r="D23" s="30" t="inlineStr">
         <is>
-          <t>SOURA ↔ LD</t>
+          <t>Soura to LD</t>
         </is>
       </c>
       <c r="E23" s="29" t="inlineStr">
@@ -3912,7 +3912,7 @@
       </c>
       <c r="D24" s="56" t="inlineStr">
         <is>
-          <t>JEHANGIR CHOWK ↔ JVC</t>
+          <t>Jehangir Chowk to JVC</t>
         </is>
       </c>
       <c r="E24" s="55" t="inlineStr">
@@ -4018,7 +4018,7 @@
       </c>
       <c r="D25" s="52" t="inlineStr">
         <is>
-          <t>JEHANGIR CHOWK ↔ JVC</t>
+          <t>Jehangir Chowk to JVC</t>
         </is>
       </c>
       <c r="E25" s="51" t="inlineStr">
@@ -4124,7 +4124,7 @@
       </c>
       <c r="D26" s="56" t="inlineStr">
         <is>
-          <t>JEHANGIR CHOWK ↔ BUDGAM</t>
+          <t>Jehangir Chowk to Budgam</t>
         </is>
       </c>
       <c r="E26" s="55" t="inlineStr">
@@ -4230,7 +4230,7 @@
       </c>
       <c r="D27" s="52" t="inlineStr">
         <is>
-          <t>JEHANGIR CHOWK ↔ JVC</t>
+          <t>Jehangir Chowk to JVC</t>
         </is>
       </c>
       <c r="E27" s="51" t="inlineStr">
@@ -4336,7 +4336,7 @@
       </c>
       <c r="D28" s="30" t="inlineStr">
         <is>
-          <t>SORA ↔ PARIMPORA</t>
+          <t>Sora to Parimpora</t>
         </is>
       </c>
       <c r="E28" s="29" t="inlineStr">
@@ -4446,7 +4446,7 @@
       </c>
       <c r="D29" s="37" t="inlineStr">
         <is>
-          <t>JEHANGIR CHOWK ↔ HMT</t>
+          <t>Jehangir Chowk to HMT</t>
         </is>
       </c>
       <c r="E29" s="36" t="inlineStr">
@@ -4552,7 +4552,7 @@
       </c>
       <c r="D30" s="30" t="inlineStr">
         <is>
-          <t>SOURA ↔ LD</t>
+          <t>Soura to LD</t>
         </is>
       </c>
       <c r="E30" s="29" t="inlineStr">
@@ -4662,7 +4662,7 @@
       </c>
       <c r="D31" s="30" t="inlineStr">
         <is>
-          <t>SOURA ↔ LD</t>
+          <t>Soura to LD</t>
         </is>
       </c>
       <c r="E31" s="29" t="inlineStr">
@@ -4772,7 +4772,7 @@
       </c>
       <c r="D32" s="47" t="inlineStr">
         <is>
-          <t>SOURA ↔ RAILWAY STATION</t>
+          <t>Soura to Railway Station</t>
         </is>
       </c>
       <c r="E32" s="46" t="inlineStr">
@@ -4878,7 +4878,7 @@
       </c>
       <c r="D33" s="30" t="inlineStr">
         <is>
-          <t>SOURA ↔ HAZRATBAL</t>
+          <t>Soura to Hazratbal</t>
         </is>
       </c>
       <c r="E33" s="29" t="inlineStr">
@@ -4988,7 +4988,7 @@
       </c>
       <c r="D34" s="30" t="inlineStr">
         <is>
-          <t>SORA ↔ LD</t>
+          <t>Sora to LD</t>
         </is>
       </c>
       <c r="E34" s="29" t="inlineStr">
@@ -5098,7 +5098,7 @@
       </c>
       <c r="D35" s="30" t="inlineStr">
         <is>
-          <t>BAGHAT SHORA ↔ LALCHOWK</t>
+          <t>Baghat Shora to Lalchowk</t>
         </is>
       </c>
       <c r="E35" s="29" t="inlineStr">
@@ -5208,7 +5208,7 @@
       </c>
       <c r="D36" s="56" t="inlineStr">
         <is>
-          <t>JEHANGIR CHOWK ↔ JVC</t>
+          <t>Jehangir Chowk to JVC</t>
         </is>
       </c>
       <c r="E36" s="55" t="inlineStr">
@@ -5314,7 +5314,7 @@
       </c>
       <c r="D37" s="52" t="inlineStr">
         <is>
-          <t>PARIMPORA ↔ RAWALPORA</t>
+          <t>Parimpora to Rawalpora</t>
         </is>
       </c>
       <c r="E37" s="51" t="inlineStr">
@@ -5420,7 +5420,7 @@
       </c>
       <c r="D38" s="56" t="inlineStr">
         <is>
-          <t>PARIMPORA ↔ RAWALPORA</t>
+          <t>Parimpora to Rawalpora</t>
         </is>
       </c>
       <c r="E38" s="55" t="inlineStr">
@@ -5526,7 +5526,7 @@
       </c>
       <c r="D39" s="52" t="inlineStr">
         <is>
-          <t>PARIMPORA ↔ RAWALPORA</t>
+          <t>Parimpora to Rawalpora</t>
         </is>
       </c>
       <c r="E39" s="51" t="inlineStr">
@@ -5632,7 +5632,7 @@
       </c>
       <c r="D40" s="30" t="inlineStr">
         <is>
-          <t>SOURA ↔ LD</t>
+          <t>Soura to LD</t>
         </is>
       </c>
       <c r="E40" s="29" t="inlineStr">
@@ -5742,7 +5742,7 @@
       </c>
       <c r="D41" s="37" t="inlineStr">
         <is>
-          <t>LALBAZAR ↔ QAMARWARI</t>
+          <t>Lalbazar to Qamarwari</t>
         </is>
       </c>
       <c r="E41" s="36" t="inlineStr">
@@ -5848,7 +5848,7 @@
       </c>
       <c r="D42" s="56" t="inlineStr">
         <is>
-          <t>NARBAL ↔ JEHANGIR CHOWK</t>
+          <t>Narbal to Jehangir Chowk</t>
         </is>
       </c>
       <c r="E42" s="55" t="inlineStr">
@@ -5954,7 +5954,7 @@
       </c>
       <c r="D43" s="30" t="inlineStr">
         <is>
-          <t>SOURA ↔ PARIMPORA</t>
+          <t>Soura to Parimpora</t>
         </is>
       </c>
       <c r="E43" s="29" t="inlineStr">
@@ -6064,7 +6064,7 @@
       </c>
       <c r="D44" s="30" t="inlineStr">
         <is>
-          <t>SOURA ↔ QAMARWARI</t>
+          <t>Soura to Qamarwari</t>
         </is>
       </c>
       <c r="E44" s="29" t="inlineStr">
@@ -6174,7 +6174,7 @@
       </c>
       <c r="D45" s="43" t="inlineStr">
         <is>
-          <t>SAFAKADAL ↔ JEHANGIR CHOWK</t>
+          <t>Safakadal to Jehangir Chowk</t>
         </is>
       </c>
       <c r="E45" s="42" t="inlineStr">
@@ -6284,7 +6284,7 @@
       </c>
       <c r="D46" s="43" t="inlineStr">
         <is>
-          <t>SAFAKADAL ↔ JEHANGIR CHOWK</t>
+          <t>Safakadal to Jehangir Chowk</t>
         </is>
       </c>
       <c r="E46" s="42" t="inlineStr">
@@ -6394,7 +6394,7 @@
       </c>
       <c r="D47" s="43" t="inlineStr">
         <is>
-          <t>SAFAKADAL ↔ JEHANGIR CHOWK</t>
+          <t>Safakadal to Jehangir Chowk</t>
         </is>
       </c>
       <c r="E47" s="42" t="inlineStr">
@@ -6504,7 +6504,7 @@
       </c>
       <c r="D48" s="30" t="inlineStr">
         <is>
-          <t>SOURA ↔ LD</t>
+          <t>Soura to LD</t>
         </is>
       </c>
       <c r="E48" s="29" t="inlineStr">
@@ -6614,7 +6614,7 @@
       </c>
       <c r="D49" s="43" t="inlineStr">
         <is>
-          <t>SAFAKADAL ↔ JEHANGIR CHOWK</t>
+          <t>Safakadal to Jehangir Chowk</t>
         </is>
       </c>
       <c r="E49" s="42" t="inlineStr">
@@ -6724,7 +6724,7 @@
       </c>
       <c r="D50" s="47" t="inlineStr">
         <is>
-          <t>LALBAZAR ↔ LD</t>
+          <t>Lalbazar to LD</t>
         </is>
       </c>
       <c r="E50" s="46" t="inlineStr">
@@ -6830,7 +6830,7 @@
       </c>
       <c r="D51" s="52" t="inlineStr">
         <is>
-          <t>QAMARWARI ↔ DALGATE</t>
+          <t>Qamarwari to Dalgate</t>
         </is>
       </c>
       <c r="E51" s="51" t="inlineStr">
@@ -6936,7 +6936,7 @@
       </c>
       <c r="D52" s="30" t="inlineStr">
         <is>
-          <t>HAZRATBAL ↔ LD</t>
+          <t>Hazratbal to LD</t>
         </is>
       </c>
       <c r="E52" s="29" t="inlineStr">
@@ -7046,7 +7046,7 @@
       </c>
       <c r="D53" s="30" t="inlineStr">
         <is>
-          <t>HAZRATBAL ↔ LD</t>
+          <t>Hazratbal to LD</t>
         </is>
       </c>
       <c r="E53" s="29" t="inlineStr">
@@ -7156,7 +7156,7 @@
       </c>
       <c r="D54" s="56" t="inlineStr">
         <is>
-          <t>QAMARWARI ↔ DALGATE</t>
+          <t>Qamarwari to Dalgate</t>
         </is>
       </c>
       <c r="E54" s="55" t="inlineStr">
@@ -7262,7 +7262,7 @@
       </c>
       <c r="D55" s="37" t="inlineStr">
         <is>
-          <t>LALBAZAR ↔ PARIMPORA</t>
+          <t>Lalbazar to Parimpora</t>
         </is>
       </c>
       <c r="E55" s="36" t="inlineStr">
@@ -7368,7 +7368,7 @@
       </c>
       <c r="D56" s="56" t="inlineStr">
         <is>
-          <t>PARIMPORA ↔ RAWALPORA</t>
+          <t>Parimpora to Rawalpora</t>
         </is>
       </c>
       <c r="E56" s="55" t="inlineStr">
@@ -7474,7 +7474,7 @@
       </c>
       <c r="D57" s="37" t="inlineStr">
         <is>
-          <t>PARIMPORA ↔ HAZRATBAL</t>
+          <t>Parimpora to Hazratbal</t>
         </is>
       </c>
       <c r="E57" s="36" t="inlineStr">
@@ -7580,7 +7580,7 @@
       </c>
       <c r="D58" s="47" t="inlineStr">
         <is>
-          <t>JEHANGIR CHOWK ↔ HMT</t>
+          <t>Jehangir Chowk to HMT</t>
         </is>
       </c>
       <c r="E58" s="46" t="inlineStr">
@@ -7686,7 +7686,7 @@
       </c>
       <c r="D59" s="37" t="inlineStr">
         <is>
-          <t>LALBAZAR ↔ PARIMPORA</t>
+          <t>Lalbazar to Parimpora</t>
         </is>
       </c>
       <c r="E59" s="36" t="inlineStr">
@@ -7792,7 +7792,7 @@
       </c>
       <c r="D60" s="47" t="inlineStr">
         <is>
-          <t>LALBAZAR ↔ PARIMPORA</t>
+          <t>Lalbazar to Parimpora</t>
         </is>
       </c>
       <c r="E60" s="46" t="inlineStr">
@@ -7898,7 +7898,7 @@
       </c>
       <c r="D61" s="37" t="inlineStr">
         <is>
-          <t>LALBAZAR ↔ PARIMPORA</t>
+          <t>Lalbazar to Parimpora</t>
         </is>
       </c>
       <c r="E61" s="36" t="inlineStr">
@@ -8004,7 +8004,7 @@
       </c>
       <c r="D62" s="47" t="inlineStr">
         <is>
-          <t>LALBAZAR ↔ PARIMPORA</t>
+          <t>Lalbazar to Parimpora</t>
         </is>
       </c>
       <c r="E62" s="46" t="inlineStr">
@@ -8110,7 +8110,7 @@
       </c>
       <c r="D63" s="37" t="inlineStr">
         <is>
-          <t>LALBAZAR ↔ PARIMPORA</t>
+          <t>Lalbazar to Parimpora</t>
         </is>
       </c>
       <c r="E63" s="36" t="inlineStr">
@@ -8216,7 +8216,7 @@
       </c>
       <c r="D64" s="47" t="inlineStr">
         <is>
-          <t>QAMARWARI ↔ HAZRATBAL</t>
+          <t>Qamarwari to Hazratbal</t>
         </is>
       </c>
       <c r="E64" s="46" t="inlineStr">
@@ -8322,7 +8322,7 @@
       </c>
       <c r="D65" s="37" t="inlineStr">
         <is>
-          <t>SOURA ↔ JEHANGIR CHOWK</t>
+          <t>Soura to Jehangir Chowk</t>
         </is>
       </c>
       <c r="E65" s="36" t="inlineStr">
@@ -8428,7 +8428,7 @@
       </c>
       <c r="D66" s="47" t="inlineStr">
         <is>
-          <t>LALBAZAR ↔ PARIMPORA</t>
+          <t>Lalbazar to Parimpora</t>
         </is>
       </c>
       <c r="E66" s="46" t="inlineStr">
@@ -8534,7 +8534,7 @@
       </c>
       <c r="D67" s="37" t="inlineStr">
         <is>
-          <t>HMT ↔ JEHANGIR CHOWK</t>
+          <t>HMT to Jehangir Chowk</t>
         </is>
       </c>
       <c r="E67" s="36" t="inlineStr">
@@ -8640,7 +8640,7 @@
       </c>
       <c r="D68" s="47" t="inlineStr">
         <is>
-          <t>LALBAZAR ↔ PARIMPORA</t>
+          <t>Lalbazar to Parimpora</t>
         </is>
       </c>
       <c r="E68" s="46" t="inlineStr">
@@ -8746,7 +8746,7 @@
       </c>
       <c r="D69" s="37" t="inlineStr">
         <is>
-          <t>SAIDAKADAL ↔ BYPASS</t>
+          <t>Saidakadal to Bypass</t>
         </is>
       </c>
       <c r="E69" s="36" t="inlineStr">
@@ -8852,7 +8852,7 @@
       </c>
       <c r="D70" s="47" t="inlineStr">
         <is>
-          <t>SAIDAKADAL ↔ BYPASS</t>
+          <t>Saidakadal to Bypass</t>
         </is>
       </c>
       <c r="E70" s="46" t="inlineStr">
@@ -8958,7 +8958,7 @@
       </c>
       <c r="D71" s="37" t="inlineStr">
         <is>
-          <t>HMT ↔ JEHANGIR CHOWK</t>
+          <t>HMT to Jehangir Chowk</t>
         </is>
       </c>
       <c r="E71" s="36" t="inlineStr">
@@ -9064,7 +9064,7 @@
       </c>
       <c r="D72" s="47" t="inlineStr">
         <is>
-          <t>JEHANGIR CHOWK ↔ HMT</t>
+          <t>Jehangir Chowk to HMT</t>
         </is>
       </c>
       <c r="E72" s="46" t="inlineStr">
@@ -9170,7 +9170,7 @@
       </c>
       <c r="D73" s="37" t="inlineStr">
         <is>
-          <t>JEHANGIR CHOWK ↔ HMT</t>
+          <t>Jehangir Chowk to HMT</t>
         </is>
       </c>
       <c r="E73" s="36" t="inlineStr">
@@ -9276,7 +9276,7 @@
       </c>
       <c r="D74" s="43" t="inlineStr">
         <is>
-          <t>SAFAKADAL ↔ JEHANGIR CHOWK</t>
+          <t>Safakadal to Jehangir Chowk</t>
         </is>
       </c>
       <c r="E74" s="42" t="inlineStr">
@@ -9386,7 +9386,7 @@
       </c>
       <c r="D75" s="43" t="inlineStr">
         <is>
-          <t>SAFAKADAL ↔ JEHANGIR CHOWK</t>
+          <t>Safakadal to Jehangir Chowk</t>
         </is>
       </c>
       <c r="E75" s="42" t="inlineStr">
@@ -9496,7 +9496,7 @@
       </c>
       <c r="D76" s="47" t="inlineStr">
         <is>
-          <t>JEHANGIR CHOWK ↔ HMT</t>
+          <t>Jehangir Chowk to HMT</t>
         </is>
       </c>
       <c r="E76" s="46" t="inlineStr">
@@ -9602,7 +9602,7 @@
       </c>
       <c r="D77" s="37" t="inlineStr">
         <is>
-          <t>JEHANGIR CHOWK ↔ PANZINARA</t>
+          <t>Jehangir Chowk to Panzinara</t>
         </is>
       </c>
       <c r="E77" s="36" t="inlineStr">
@@ -9708,7 +9708,7 @@
       </c>
       <c r="D78" s="43" t="inlineStr">
         <is>
-          <t>SAFAKADAL ↔ JEHANGIR CHOWK</t>
+          <t>Safakadal to Jehangir Chowk</t>
         </is>
       </c>
       <c r="E78" s="42" t="inlineStr">
@@ -9818,7 +9818,7 @@
       </c>
       <c r="D79" s="43" t="inlineStr">
         <is>
-          <t>SAFAKADAL ↔ JEHANGIR CHOWK</t>
+          <t>Safakadal to Jehangir Chowk</t>
         </is>
       </c>
       <c r="E79" s="42" t="inlineStr">
@@ -9928,7 +9928,7 @@
       </c>
       <c r="D80" s="43" t="inlineStr">
         <is>
-          <t>SAFAKADAL ↔ JEHANGIR CHOWK</t>
+          <t>Safakadal to Jehangir Chowk</t>
         </is>
       </c>
       <c r="E80" s="42" t="inlineStr">
@@ -10038,7 +10038,7 @@
       </c>
       <c r="D81" s="43" t="inlineStr">
         <is>
-          <t>SAFAKADAL ↔ JEHANGIR CHOWK</t>
+          <t>Safakadal to Jehangir Chowk</t>
         </is>
       </c>
       <c r="E81" s="42" t="inlineStr">
@@ -10148,7 +10148,7 @@
       </c>
       <c r="D82" s="56" t="inlineStr">
         <is>
-          <t>PARIMPORA ↔ RAWALPORA</t>
+          <t>Parimpora to Rawalpora</t>
         </is>
       </c>
       <c r="E82" s="55" t="inlineStr">
@@ -10254,7 +10254,7 @@
       </c>
       <c r="D83" s="52" t="inlineStr">
         <is>
-          <t>JEHANGIR CHOWK ↔ JVC</t>
+          <t>Jehangir Chowk to JVC</t>
         </is>
       </c>
       <c r="E83" s="51" t="inlineStr">
@@ -10360,7 +10360,7 @@
       </c>
       <c r="D84" s="47" t="inlineStr">
         <is>
-          <t>JEHANGIR CHOWK ↔ HMT</t>
+          <t>Jehangir Chowk to HMT</t>
         </is>
       </c>
       <c r="E84" s="46" t="inlineStr">
@@ -10466,7 +10466,7 @@
       </c>
       <c r="D85" s="52" t="inlineStr">
         <is>
-          <t>JEHANGIR CHOWK ↔ BUDGAM</t>
+          <t>Jehangir Chowk to Budgam</t>
         </is>
       </c>
       <c r="E85" s="51" t="inlineStr">
@@ -10572,7 +10572,7 @@
       </c>
       <c r="D86" s="47" t="inlineStr">
         <is>
-          <t>LALBAZAR ↔ PARIMPORA</t>
+          <t>Lalbazar to Parimpora</t>
         </is>
       </c>
       <c r="E86" s="46" t="inlineStr">
@@ -10678,7 +10678,7 @@
       </c>
       <c r="D87" s="37" t="inlineStr">
         <is>
-          <t>SOURA ↔ JEHANGIR CHOWK</t>
+          <t>Soura to Jehangir Chowk</t>
         </is>
       </c>
       <c r="E87" s="36" t="inlineStr">
@@ -10784,7 +10784,7 @@
       </c>
       <c r="D88" s="47" t="inlineStr">
         <is>
-          <t>SOURA ↔ JEHANGIR CHOWK</t>
+          <t>Soura to Jehangir Chowk</t>
         </is>
       </c>
       <c r="E88" s="46" t="inlineStr">
@@ -10890,7 +10890,7 @@
       </c>
       <c r="D89" s="43" t="inlineStr">
         <is>
-          <t>QAMARWARI ↔ JEHANGIR CHOWK</t>
+          <t>Qamarwari to Jehangir Chowk</t>
         </is>
       </c>
       <c r="E89" s="42" t="inlineStr">
@@ -11000,7 +11000,7 @@
       </c>
       <c r="D90" s="56" t="inlineStr">
         <is>
-          <t>NARBAL ↔ JEHANGIR CHOWK</t>
+          <t>Narbal to Jehangir Chowk</t>
         </is>
       </c>
       <c r="E90" s="55" t="inlineStr">
@@ -11106,7 +11106,7 @@
       </c>
       <c r="D91" s="52" t="inlineStr">
         <is>
-          <t>QAMARWARI ↔ DALGATE</t>
+          <t>Qamarwari to Dalgate</t>
         </is>
       </c>
       <c r="E91" s="51" t="inlineStr">
@@ -11212,7 +11212,7 @@
       </c>
       <c r="D92" s="43" t="inlineStr">
         <is>
-          <t>PARIMPORA ↔ JEHANGIR CHOWK</t>
+          <t>Parimpora to Jehangir Chowk</t>
         </is>
       </c>
       <c r="E92" s="42" t="inlineStr">
@@ -11322,7 +11322,7 @@
       </c>
       <c r="D93" s="52" t="inlineStr">
         <is>
-          <t>QAMARWARI ↔ DALGATE</t>
+          <t>Qamarwari to Dalgate</t>
         </is>
       </c>
       <c r="E93" s="51" t="inlineStr">
@@ -11428,7 +11428,7 @@
       </c>
       <c r="D94" s="47" t="inlineStr">
         <is>
-          <t>SOURA ↔ JEHANGIR CHOWK</t>
+          <t>Soura to Jehangir Chowk</t>
         </is>
       </c>
       <c r="E94" s="46" t="inlineStr">
@@ -11534,7 +11534,7 @@
       </c>
       <c r="D95" s="37" t="inlineStr">
         <is>
-          <t>LALBAZAR ↔ LD</t>
+          <t>Lalbazar to LD</t>
         </is>
       </c>
       <c r="E95" s="36" t="inlineStr">
@@ -11640,7 +11640,7 @@
       </c>
       <c r="D96" s="47" t="inlineStr">
         <is>
-          <t>LALBAZAR ↔ LD</t>
+          <t>Lalbazar to LD</t>
         </is>
       </c>
       <c r="E96" s="46" t="inlineStr">
@@ -11746,7 +11746,7 @@
       </c>
       <c r="D97" s="37" t="inlineStr">
         <is>
-          <t>LALBAZAR ↔ LD</t>
+          <t>Lalbazar to LD</t>
         </is>
       </c>
       <c r="E97" s="36" t="inlineStr">
@@ -11852,7 +11852,7 @@
       </c>
       <c r="D98" s="56" t="inlineStr">
         <is>
-          <t>JVC ↔ BATWARA</t>
+          <t>JVC to Batwara</t>
         </is>
       </c>
       <c r="E98" s="55" t="inlineStr">
@@ -11958,7 +11958,7 @@
       </c>
       <c r="D99" s="52" t="inlineStr">
         <is>
-          <t>NARBAL ↔ JEHANGIR CHOWK</t>
+          <t>Narbal to Jehangir Chowk</t>
         </is>
       </c>
       <c r="E99" s="51" t="inlineStr">
@@ -12064,7 +12064,7 @@
       </c>
       <c r="D100" s="56" t="inlineStr">
         <is>
-          <t>QAMARWARI ↔ DALGATE</t>
+          <t>Qamarwari to Dalgate</t>
         </is>
       </c>
       <c r="E100" s="55" t="inlineStr">
@@ -12170,7 +12170,7 @@
       </c>
       <c r="D101" s="43" t="inlineStr">
         <is>
-          <t>SAFAKADAL ↔ JEHANGIR CHOWK</t>
+          <t>Safakadal to Jehangir Chowk</t>
         </is>
       </c>
       <c r="E101" s="42" t="inlineStr">
@@ -12280,7 +12280,7 @@
       </c>
       <c r="D102" s="47" t="inlineStr">
         <is>
-          <t>HAZRATBAL ↔ BONE JOINT HOSPITAL BARZALLA</t>
+          <t>Hazratbal to Bone Joint Hospital Barzalla</t>
         </is>
       </c>
       <c r="E102" s="46" t="inlineStr">
@@ -12386,7 +12386,7 @@
       </c>
       <c r="D103" s="30" t="inlineStr">
         <is>
-          <t>HAZRATBAL ↔ LD</t>
+          <t>Hazratbal to LD</t>
         </is>
       </c>
       <c r="E103" s="29" t="inlineStr">
@@ -12496,7 +12496,7 @@
       </c>
       <c r="D104" s="30" t="inlineStr">
         <is>
-          <t>HAZRATBAL ↔ LD</t>
+          <t>Hazratbal to LD</t>
         </is>
       </c>
       <c r="E104" s="29" t="inlineStr">
@@ -12606,7 +12606,7 @@
       </c>
       <c r="D105" s="43" t="inlineStr">
         <is>
-          <t>GBS ↔ LAL CHOWK</t>
+          <t>GBS to LAL Chowk</t>
         </is>
       </c>
       <c r="E105" s="42" t="inlineStr">
@@ -12716,7 +12716,7 @@
       </c>
       <c r="D106" s="56" t="inlineStr">
         <is>
-          <t>PARIMPORA ↔ JAWAHAIRNAGAR</t>
+          <t>Parimpora to Jawahairnagar</t>
         </is>
       </c>
       <c r="E106" s="55" t="inlineStr">
@@ -12822,7 +12822,7 @@
       </c>
       <c r="D107" s="52" t="inlineStr">
         <is>
-          <t>QAMARWARI ↔ DALGATE</t>
+          <t>Qamarwari to Dalgate</t>
         </is>
       </c>
       <c r="E107" s="51" t="inlineStr">
@@ -12928,7 +12928,7 @@
       </c>
       <c r="D108" s="43" t="inlineStr">
         <is>
-          <t>PARIMPORA ↔ JAWAHAIRNAGAR</t>
+          <t>Parimpora to Jawahairnagar</t>
         </is>
       </c>
       <c r="E108" s="42" t="inlineStr">
@@ -13038,7 +13038,7 @@
       </c>
       <c r="D109" s="52" t="inlineStr">
         <is>
-          <t>QAMARWARI ↔ BAGHI MEHTAB</t>
+          <t>Qamarwari to Baghi Mehtab</t>
         </is>
       </c>
       <c r="E109" s="51" t="inlineStr">
@@ -13144,7 +13144,7 @@
       </c>
       <c r="D110" s="47" t="inlineStr">
         <is>
-          <t>LALBAZAR ↔ LD</t>
+          <t>Lalbazar to LD</t>
         </is>
       </c>
       <c r="E110" s="46" t="inlineStr">
@@ -13250,7 +13250,7 @@
       </c>
       <c r="D111" s="37" t="inlineStr">
         <is>
-          <t>LALBAZAR ↔ LD</t>
+          <t>Lalbazar to LD</t>
         </is>
       </c>
       <c r="E111" s="36" t="inlineStr">
@@ -13356,7 +13356,7 @@
       </c>
       <c r="D112" s="47" t="inlineStr">
         <is>
-          <t>LALBAZAR ↔ LD</t>
+          <t>Lalbazar to LD</t>
         </is>
       </c>
       <c r="E112" s="46" t="inlineStr">
@@ -13462,7 +13462,7 @@
       </c>
       <c r="D113" s="30" t="inlineStr">
         <is>
-          <t>HAZRATBAL ↔ LD</t>
+          <t>Hazratbal to LD</t>
         </is>
       </c>
       <c r="E113" s="29" t="inlineStr">
@@ -13572,7 +13572,7 @@
       </c>
       <c r="D114" s="47" t="inlineStr">
         <is>
-          <t>JEHANGIR CHOWK ↔ BEMINA</t>
+          <t>Jehangir Chowk to Bemina</t>
         </is>
       </c>
       <c r="E114" s="46" t="inlineStr">
@@ -13678,7 +13678,7 @@
       </c>
       <c r="D115" s="30" t="inlineStr">
         <is>
-          <t>HAZRATBAL ↔ LD</t>
+          <t>Hazratbal to LD</t>
         </is>
       </c>
       <c r="E115" s="29" t="inlineStr">
@@ -13788,7 +13788,7 @@
       </c>
       <c r="D116" s="43" t="inlineStr">
         <is>
-          <t>PARIMPORA ↔ JAWAHIRNAGAR</t>
+          <t>Parimpora to Jawahirnagar</t>
         </is>
       </c>
       <c r="E116" s="42" t="inlineStr">
@@ -13898,7 +13898,7 @@
       </c>
       <c r="D117" s="30" t="inlineStr">
         <is>
-          <t>HAZRATBAL ↔ LD</t>
+          <t>Hazratbal to LD</t>
         </is>
       </c>
       <c r="E117" s="29" t="inlineStr">
@@ -14008,7 +14008,7 @@
       </c>
       <c r="D118" s="30" t="inlineStr">
         <is>
-          <t>HAZRATBAL ↔ LD</t>
+          <t>Hazratbal to LD</t>
         </is>
       </c>
       <c r="E118" s="29" t="inlineStr">
@@ -14118,7 +14118,7 @@
       </c>
       <c r="D119" s="30" t="inlineStr">
         <is>
-          <t>HAZRATBAL ↔ LD</t>
+          <t>Hazratbal to LD</t>
         </is>
       </c>
       <c r="E119" s="29" t="inlineStr">
@@ -14228,7 +14228,7 @@
       </c>
       <c r="D120" s="43" t="inlineStr">
         <is>
-          <t>PARIMPORA ↔ JAWAHIRNAGAR</t>
+          <t>Parimpora to Jawahirnagar</t>
         </is>
       </c>
       <c r="E120" s="42" t="inlineStr">
@@ -14338,7 +14338,7 @@
       </c>
       <c r="D121" s="30" t="inlineStr">
         <is>
-          <t>JEHANGIR CHOWK ↔ BEMINA</t>
+          <t>Jehangir Chowk to Bemina</t>
         </is>
       </c>
       <c r="E121" s="29" t="inlineStr">
@@ -14448,7 +14448,7 @@
       </c>
       <c r="D122" s="43" t="inlineStr">
         <is>
-          <t>SAFAKADAL ↔ JEHANGIR CHOWK</t>
+          <t>Safakadal to Jehangir Chowk</t>
         </is>
       </c>
       <c r="E122" s="42" t="inlineStr">
@@ -14558,7 +14558,7 @@
       </c>
       <c r="D123" s="43" t="inlineStr">
         <is>
-          <t>PARIMPORA ↔ JAWAHIRNAGAR</t>
+          <t>Parimpora to Jawahirnagar</t>
         </is>
       </c>
       <c r="E123" s="42" t="inlineStr">
@@ -14668,7 +14668,7 @@
       </c>
       <c r="D124" s="30" t="inlineStr">
         <is>
-          <t>HAZRATBAL ↔ LD</t>
+          <t>Hazratbal to LD</t>
         </is>
       </c>
       <c r="E124" s="29" t="inlineStr">
@@ -14778,7 +14778,7 @@
       </c>
       <c r="D125" s="30" t="inlineStr">
         <is>
-          <t>HAZRATBAL ↔ LD</t>
+          <t>Hazratbal to LD</t>
         </is>
       </c>
       <c r="E125" s="29" t="inlineStr">
@@ -14888,7 +14888,7 @@
       </c>
       <c r="D126" s="30" t="inlineStr">
         <is>
-          <t>HAZRATBAL ↔ LD</t>
+          <t>Hazratbal to LD</t>
         </is>
       </c>
       <c r="E126" s="29" t="inlineStr">
@@ -14998,7 +14998,7 @@
       </c>
       <c r="D127" s="37" t="inlineStr">
         <is>
-          <t>JEHANGIR CHOWK ↔ HMT</t>
+          <t>Jehangir Chowk to HMT</t>
         </is>
       </c>
       <c r="E127" s="36" t="inlineStr">
@@ -15104,7 +15104,7 @@
       </c>
       <c r="D128" s="56" t="inlineStr">
         <is>
-          <t>QAMARWARI ↔ DALGATE</t>
+          <t>Qamarwari to Dalgate</t>
         </is>
       </c>
       <c r="E128" s="55" t="inlineStr">
@@ -15210,7 +15210,7 @@
       </c>
       <c r="D129" s="37" t="inlineStr">
         <is>
-          <t>LALBAZAR ↔ LALCHOWK</t>
+          <t>Lalbazar to Lalchowk</t>
         </is>
       </c>
       <c r="E129" s="36" t="inlineStr">
@@ -15316,7 +15316,7 @@
       </c>
       <c r="D130" s="30" t="inlineStr">
         <is>
-          <t>SOURA ↔ PARIMPORA</t>
+          <t>Soura to Parimpora</t>
         </is>
       </c>
       <c r="E130" s="29" t="inlineStr">
@@ -15426,7 +15426,7 @@
       </c>
       <c r="D131" s="30" t="inlineStr">
         <is>
-          <t>HAZRATBAL ↔ LD</t>
+          <t>Hazratbal to LD</t>
         </is>
       </c>
       <c r="E131" s="29" t="inlineStr">
@@ -15536,7 +15536,7 @@
       </c>
       <c r="D132" s="47" t="inlineStr">
         <is>
-          <t>CHANAPORA ↔ SOURA</t>
+          <t>Chanapora to Soura</t>
         </is>
       </c>
       <c r="E132" s="46" t="inlineStr">
@@ -15642,7 +15642,7 @@
       </c>
       <c r="D133" s="43" t="inlineStr">
         <is>
-          <t>SAFAKADAL ↔ JEHANGIR CHOWK</t>
+          <t>Safakadal to Jehangir Chowk</t>
         </is>
       </c>
       <c r="E133" s="42" t="inlineStr">
@@ -15752,7 +15752,7 @@
       </c>
       <c r="D134" s="47" t="inlineStr">
         <is>
-          <t>SOURA ↔ GANDERBAL</t>
+          <t>Soura to Ganderbal</t>
         </is>
       </c>
       <c r="E134" s="46" t="inlineStr">
@@ -15858,7 +15858,7 @@
       </c>
       <c r="D135" s="52" t="inlineStr">
         <is>
-          <t>JEHANGIR CHOWK ↔ BUDGAM</t>
+          <t>Jehangir Chowk to Budgam</t>
         </is>
       </c>
       <c r="E135" s="51" t="inlineStr">
@@ -15964,7 +15964,7 @@
       </c>
       <c r="D136" s="47" t="inlineStr">
         <is>
-          <t>JEHANGIR CHOWK ↔ HMT</t>
+          <t>Jehangir Chowk to HMT</t>
         </is>
       </c>
       <c r="E136" s="46" t="inlineStr">
@@ -16070,7 +16070,7 @@
       </c>
       <c r="D137" s="52" t="inlineStr">
         <is>
-          <t>JEHANGIR CHOWK ↔ BUDGAM</t>
+          <t>Jehangir Chowk to Budgam</t>
         </is>
       </c>
       <c r="E137" s="51" t="inlineStr">
@@ -16176,7 +16176,7 @@
       </c>
       <c r="D138" s="47" t="inlineStr">
         <is>
-          <t>SOURA ↔ JEHANGIR CHOWK</t>
+          <t>Soura to Jehangir Chowk</t>
         </is>
       </c>
       <c r="E138" s="46" t="inlineStr">
@@ -16282,7 +16282,7 @@
       </c>
       <c r="D139" s="30" t="inlineStr">
         <is>
-          <t>HAZRATBAL ↔ LD</t>
+          <t>Hazratbal to LD</t>
         </is>
       </c>
       <c r="E139" s="29" t="inlineStr">
@@ -16392,7 +16392,7 @@
       </c>
       <c r="D140" s="30" t="inlineStr">
         <is>
-          <t>HAZRATBAL ↔ LD</t>
+          <t>Hazratbal to LD</t>
         </is>
       </c>
       <c r="E140" s="29" t="inlineStr">
@@ -16502,7 +16502,7 @@
       </c>
       <c r="D141" s="37" t="inlineStr">
         <is>
-          <t>BATMALOO ↔ DALGATE</t>
+          <t>Batmaloo to Dalgate</t>
         </is>
       </c>
       <c r="E141" s="36" t="inlineStr">
@@ -16608,7 +16608,7 @@
       </c>
       <c r="D142" s="47" t="inlineStr">
         <is>
-          <t>LALBAZAR ↔ LALCHOWK</t>
+          <t>Lalbazar to Lalchowk</t>
         </is>
       </c>
       <c r="E142" s="46" t="inlineStr">
@@ -16714,7 +16714,7 @@
       </c>
       <c r="D143" s="43" t="inlineStr">
         <is>
-          <t>SAFAKADAL ↔ JEHANGIR CHOWK</t>
+          <t>Safakadal to Jehangir Chowk</t>
         </is>
       </c>
       <c r="E143" s="42" t="inlineStr">
@@ -16824,7 +16824,7 @@
       </c>
       <c r="D144" s="56" t="inlineStr">
         <is>
-          <t>JEHANGIR CHOWK ↔ BUDGAM</t>
+          <t>Jehangir Chowk to Budgam</t>
         </is>
       </c>
       <c r="E144" s="55" t="inlineStr">
@@ -16930,7 +16930,7 @@
       </c>
       <c r="D145" s="43" t="inlineStr">
         <is>
-          <t>SAFAKADAL ↔ JEHANGIR CHOWK</t>
+          <t>Safakadal to Jehangir Chowk</t>
         </is>
       </c>
       <c r="E145" s="42" t="inlineStr">
@@ -17040,7 +17040,7 @@
       </c>
       <c r="D146" s="30" t="inlineStr">
         <is>
-          <t>HAZRATBAL ↔ LD</t>
+          <t>Hazratbal to LD</t>
         </is>
       </c>
       <c r="E146" s="29" t="inlineStr">
@@ -17150,7 +17150,7 @@
       </c>
       <c r="D147" s="37" t="inlineStr">
         <is>
-          <t>HMT ↔ JEHANGIR CHOWK</t>
+          <t>HMT to Jehangir Chowk</t>
         </is>
       </c>
       <c r="E147" s="36" t="inlineStr">
@@ -17256,7 +17256,7 @@
       </c>
       <c r="D148" s="56" t="inlineStr">
         <is>
-          <t>NARBAL ↔ JEHANGIR CHOWK</t>
+          <t>Narbal to Jehangir Chowk</t>
         </is>
       </c>
       <c r="E148" s="55" t="inlineStr">
@@ -17362,7 +17362,7 @@
       </c>
       <c r="D149" s="30" t="inlineStr">
         <is>
-          <t>HAZRATBAL ↔ LD</t>
+          <t>Hazratbal to LD</t>
         </is>
       </c>
       <c r="E149" s="29" t="inlineStr">
@@ -17472,7 +17472,7 @@
       </c>
       <c r="D150" s="30" t="inlineStr">
         <is>
-          <t>HAZRATBAL ↔ LD</t>
+          <t>Hazratbal to LD</t>
         </is>
       </c>
       <c r="E150" s="29" t="inlineStr">
@@ -17582,7 +17582,7 @@
       </c>
       <c r="D151" s="52" t="inlineStr">
         <is>
-          <t>JEHANGIR CHOWK ↔ JVC</t>
+          <t>Jehangir Chowk to JVC</t>
         </is>
       </c>
       <c r="E151" s="51" t="inlineStr">
@@ -17688,7 +17688,7 @@
       </c>
       <c r="D152" s="30" t="inlineStr">
         <is>
-          <t>JEHANGIR CHOWK ↔ BEMINA</t>
+          <t>Jehangir Chowk to Bemina</t>
         </is>
       </c>
       <c r="E152" s="29" t="inlineStr">
@@ -17798,7 +17798,7 @@
       </c>
       <c r="D153" s="30" t="inlineStr">
         <is>
-          <t>HAZRATBAL ↔ LD</t>
+          <t>Hazratbal to LD</t>
         </is>
       </c>
       <c r="E153" s="29" t="inlineStr">
@@ -17908,7 +17908,7 @@
       </c>
       <c r="D154" s="30" t="inlineStr">
         <is>
-          <t>HAZRATBAL ↔ LD</t>
+          <t>Hazratbal to LD</t>
         </is>
       </c>
       <c r="E154" s="29" t="inlineStr">
@@ -18018,7 +18018,7 @@
       </c>
       <c r="D155" s="43" t="inlineStr">
         <is>
-          <t>PARIMPORA ↔ JAWAHIRNAGAR</t>
+          <t>Parimpora to Jawahirnagar</t>
         </is>
       </c>
       <c r="E155" s="42" t="inlineStr">
@@ -18128,7 +18128,7 @@
       </c>
       <c r="D156" s="30" t="inlineStr">
         <is>
-          <t>HAZRATBAL ↔ LD</t>
+          <t>Hazratbal to LD</t>
         </is>
       </c>
       <c r="E156" s="29" t="inlineStr">
@@ -18238,7 +18238,7 @@
       </c>
       <c r="D157" s="30" t="inlineStr">
         <is>
-          <t>JEHANGIR CHOWK ↔ BEMINA</t>
+          <t>Jehangir Chowk to Bemina</t>
         </is>
       </c>
       <c r="E157" s="29" t="inlineStr">
@@ -18348,7 +18348,7 @@
       </c>
       <c r="D158" s="30" t="inlineStr">
         <is>
-          <t>HAZRATBAL ↔ LD</t>
+          <t>Hazratbal to LD</t>
         </is>
       </c>
       <c r="E158" s="29" t="inlineStr">
@@ -18458,7 +18458,7 @@
       </c>
       <c r="D159" s="30" t="inlineStr">
         <is>
-          <t>SOURA ↔ HAZRATBAL</t>
+          <t>Soura to Hazratbal</t>
         </is>
       </c>
       <c r="E159" s="29" t="inlineStr">
@@ -18568,7 +18568,7 @@
       </c>
       <c r="D160" s="47" t="inlineStr">
         <is>
-          <t>PARIMPORA ↔ HAZRATBAL</t>
+          <t>Parimpora to Hazratbal</t>
         </is>
       </c>
       <c r="E160" s="46" t="inlineStr">
@@ -18674,7 +18674,7 @@
       </c>
       <c r="D161" s="30" t="inlineStr">
         <is>
-          <t>JEHANGIR CHOWK ↔ BEMINA</t>
+          <t>Jehangir Chowk to Bemina</t>
         </is>
       </c>
       <c r="E161" s="29" t="inlineStr">
@@ -18784,7 +18784,7 @@
       </c>
       <c r="D162" s="47" t="inlineStr">
         <is>
-          <t>PARIMPORA ↔ HAZRATBAL</t>
+          <t>Parimpora to Hazratbal</t>
         </is>
       </c>
       <c r="E162" s="46" t="inlineStr">
@@ -18890,7 +18890,7 @@
       </c>
       <c r="D163" s="37" t="inlineStr">
         <is>
-          <t>SOURA ↔ DALGATE</t>
+          <t>Soura to Dalgate</t>
         </is>
       </c>
       <c r="E163" s="36" t="inlineStr">
@@ -18996,7 +18996,7 @@
       </c>
       <c r="D164" s="47" t="inlineStr">
         <is>
-          <t>SOURA ↔ JEHANGIR CHOWK</t>
+          <t>Soura to Jehangir Chowk</t>
         </is>
       </c>
       <c r="E164" s="46" t="inlineStr">
@@ -19102,7 +19102,7 @@
       </c>
       <c r="D165" s="37" t="inlineStr">
         <is>
-          <t>JEHANGIR CHOWK ↔ HMT</t>
+          <t>Jehangir Chowk to HMT</t>
         </is>
       </c>
       <c r="E165" s="36" t="inlineStr">
@@ -19208,7 +19208,7 @@
       </c>
       <c r="D166" s="30" t="inlineStr">
         <is>
-          <t>HAZRATBAL ↔ LD</t>
+          <t>Hazratbal to LD</t>
         </is>
       </c>
       <c r="E166" s="29" t="inlineStr">
@@ -19318,7 +19318,7 @@
       </c>
       <c r="D167" s="30" t="inlineStr">
         <is>
-          <t>HAZRATBAL ↔ LD</t>
+          <t>Hazratbal to LD</t>
         </is>
       </c>
       <c r="E167" s="29" t="inlineStr">
@@ -19428,7 +19428,7 @@
       </c>
       <c r="D168" s="47" t="inlineStr">
         <is>
-          <t>SOURA ↔ JEHANGIR CHOWK</t>
+          <t>Soura to Jehangir Chowk</t>
         </is>
       </c>
       <c r="E168" s="46" t="inlineStr">
@@ -19534,7 +19534,7 @@
       </c>
       <c r="D169" s="30" t="inlineStr">
         <is>
-          <t>JEHANGIR CHOWK ↔ BEMINA</t>
+          <t>Jehangir Chowk to Bemina</t>
         </is>
       </c>
       <c r="E169" s="29" t="inlineStr">
@@ -19644,7 +19644,7 @@
       </c>
       <c r="D170" s="30" t="inlineStr">
         <is>
-          <t>SOURA ↔ CHUNTWALIWAR</t>
+          <t>Soura to Chuntwaliwar</t>
         </is>
       </c>
       <c r="E170" s="29" t="inlineStr">
@@ -19754,7 +19754,7 @@
       </c>
       <c r="D171" s="37" t="inlineStr">
         <is>
-          <t>JEHANGIR CHOWK ↔ HMT</t>
+          <t>Jehangir Chowk to HMT</t>
         </is>
       </c>
       <c r="E171" s="36" t="inlineStr">
@@ -19860,7 +19860,7 @@
       </c>
       <c r="D172" s="56" t="inlineStr">
         <is>
-          <t>JEHANGIR CHOWK ↔ JVC</t>
+          <t>Jehangir Chowk to JVC</t>
         </is>
       </c>
       <c r="E172" s="55" t="inlineStr">
@@ -19966,7 +19966,7 @@
       </c>
       <c r="D173" s="37" t="inlineStr">
         <is>
-          <t>HMT ↔ JEHANGIR CHOWK</t>
+          <t>HMT to Jehangir Chowk</t>
         </is>
       </c>
       <c r="E173" s="36" t="inlineStr">
@@ -20072,7 +20072,7 @@
       </c>
       <c r="D174" s="47" t="inlineStr">
         <is>
-          <t>SOURA ↔ BATAMALLO</t>
+          <t>Soura to Batamallo</t>
         </is>
       </c>
       <c r="E174" s="46" t="inlineStr">
@@ -20178,7 +20178,7 @@
       </c>
       <c r="D175" s="30" t="inlineStr">
         <is>
-          <t>JEHANGIR CHOWK ↔ BEMINA</t>
+          <t>Jehangir Chowk to Bemina</t>
         </is>
       </c>
       <c r="E175" s="29" t="inlineStr">
@@ -20288,7 +20288,7 @@
       </c>
       <c r="D176" s="30" t="inlineStr">
         <is>
-          <t>SOURA ↔ PARIMPORA</t>
+          <t>Soura to Parimpora</t>
         </is>
       </c>
       <c r="E176" s="29" t="inlineStr">
@@ -20398,7 +20398,7 @@
       </c>
       <c r="D177" s="37" t="inlineStr">
         <is>
-          <t>RANGPORA ↔ SOURA</t>
+          <t>Rangpora to Soura</t>
         </is>
       </c>
       <c r="E177" s="36" t="inlineStr">
@@ -20504,7 +20504,7 @@
       </c>
       <c r="D178" s="47" t="inlineStr">
         <is>
-          <t>RANGPORA ↔ SOURA</t>
+          <t>Rangpora to Soura</t>
         </is>
       </c>
       <c r="E178" s="46" t="inlineStr">
@@ -20610,7 +20610,7 @@
       </c>
       <c r="D179" s="30" t="inlineStr">
         <is>
-          <t>HAZRATBAL ↔ LD</t>
+          <t>Hazratbal to LD</t>
         </is>
       </c>
       <c r="E179" s="29" t="inlineStr">
@@ -20720,7 +20720,7 @@
       </c>
       <c r="D180" s="30" t="inlineStr">
         <is>
-          <t>HAZRATBAL ↔ LD</t>
+          <t>Hazratbal to LD</t>
         </is>
       </c>
       <c r="E180" s="29" t="inlineStr">
@@ -20830,7 +20830,7 @@
       </c>
       <c r="D181" s="37" t="inlineStr">
         <is>
-          <t>JEHANGIR CHOWK ↔ PANZINARA</t>
+          <t>Jehangir Chowk to Panzinara</t>
         </is>
       </c>
       <c r="E181" s="36" t="inlineStr">
@@ -20936,7 +20936,7 @@
       </c>
       <c r="D182" s="30" t="inlineStr">
         <is>
-          <t>HAZRATBAL ↔ LD</t>
+          <t>Hazratbal to LD</t>
         </is>
       </c>
       <c r="E182" s="29" t="inlineStr">
@@ -21046,7 +21046,7 @@
       </c>
       <c r="D183" s="52" t="inlineStr">
         <is>
-          <t>JEHANGIR CHOWK ↔ BUDGAM</t>
+          <t>Jehangir Chowk to Budgam</t>
         </is>
       </c>
       <c r="E183" s="51" t="inlineStr">
@@ -21152,7 +21152,7 @@
       </c>
       <c r="D184" s="56" t="inlineStr">
         <is>
-          <t>NARBAL ↔ JEHANGIR CHOWK</t>
+          <t>Narbal to Jehangir Chowk</t>
         </is>
       </c>
       <c r="E184" s="55" t="inlineStr">
@@ -21258,7 +21258,7 @@
       </c>
       <c r="D185" s="52" t="inlineStr">
         <is>
-          <t>JEHANGIR CHOWK ↔ BUDGAM</t>
+          <t>Jehangir Chowk to Budgam</t>
         </is>
       </c>
       <c r="E185" s="51" t="inlineStr">
@@ -21364,7 +21364,7 @@
       </c>
       <c r="D186" s="47" t="inlineStr">
         <is>
-          <t>RANGPORA ↔ SOURA</t>
+          <t>Rangpora to Soura</t>
         </is>
       </c>
       <c r="E186" s="46" t="inlineStr">
@@ -21470,7 +21470,7 @@
       </c>
       <c r="D187" s="37" t="inlineStr">
         <is>
-          <t>JEHANGIR CHOWK ↔ HMT</t>
+          <t>Jehangir Chowk to HMT</t>
         </is>
       </c>
       <c r="E187" s="36" t="inlineStr">
@@ -21576,7 +21576,7 @@
       </c>
       <c r="D188" s="47" t="inlineStr">
         <is>
-          <t>SOURA ↔ JEHANGIR CHOWK</t>
+          <t>Soura to Jehangir Chowk</t>
         </is>
       </c>
       <c r="E188" s="46" t="inlineStr">
@@ -21682,7 +21682,7 @@
       </c>
       <c r="D189" s="30" t="inlineStr">
         <is>
-          <t>HAZRATBAL ↔ LD</t>
+          <t>Hazratbal to LD</t>
         </is>
       </c>
       <c r="E189" s="29" t="inlineStr">
@@ -21792,7 +21792,7 @@
       </c>
       <c r="D190" s="47" t="inlineStr">
         <is>
-          <t>LALBAZAR ↔ LALCHOWK</t>
+          <t>Lalbazar to Lalchowk</t>
         </is>
       </c>
       <c r="E190" s="46" t="inlineStr">
@@ -21898,7 +21898,7 @@
       </c>
       <c r="D191" s="52" t="inlineStr">
         <is>
-          <t>RANGPORA ↔ DALGATE</t>
+          <t>Rangpora to Dalgate</t>
         </is>
       </c>
       <c r="E191" s="51" t="inlineStr">
@@ -22004,7 +22004,7 @@
       </c>
       <c r="D192" s="30" t="inlineStr">
         <is>
-          <t>JEHANGIR CHOWK ↔ BEMINA</t>
+          <t>Jehangir Chowk to Bemina</t>
         </is>
       </c>
       <c r="E192" s="29" t="inlineStr">
@@ -22114,7 +22114,7 @@
       </c>
       <c r="D193" s="37" t="inlineStr">
         <is>
-          <t>SOURA ↔ JEHANGIR CHOWK</t>
+          <t>Soura to Jehangir Chowk</t>
         </is>
       </c>
       <c r="E193" s="36" t="inlineStr">
@@ -22220,7 +22220,7 @@
       </c>
       <c r="D194" s="47" t="inlineStr">
         <is>
-          <t>LALBAZAR ↔ LALCHOWK</t>
+          <t>Lalbazar to Lalchowk</t>
         </is>
       </c>
       <c r="E194" s="46" t="inlineStr">
@@ -22326,7 +22326,7 @@
       </c>
       <c r="D195" s="30" t="inlineStr">
         <is>
-          <t>JEHANGIR CHOWK ↔ BEMINA</t>
+          <t>Jehangir Chowk to Bemina</t>
         </is>
       </c>
       <c r="E195" s="29" t="inlineStr">
@@ -22436,7 +22436,7 @@
       </c>
       <c r="D196" s="56" t="inlineStr">
         <is>
-          <t>NARBAL ↔ JEHANGIR CHOWK</t>
+          <t>Narbal to Jehangir Chowk</t>
         </is>
       </c>
       <c r="E196" s="55" t="inlineStr">
@@ -22542,7 +22542,7 @@
       </c>
       <c r="D197" s="37" t="inlineStr">
         <is>
-          <t>SOURA ↔ JEHANGIR CHOWK</t>
+          <t>Soura to Jehangir Chowk</t>
         </is>
       </c>
       <c r="E197" s="36" t="inlineStr">
@@ -22648,7 +22648,7 @@
       </c>
       <c r="D198" s="47" t="inlineStr">
         <is>
-          <t>SOURA ↔ JEHANGIR CHOWK</t>
+          <t>Soura to Jehangir Chowk</t>
         </is>
       </c>
       <c r="E198" s="46" t="inlineStr">
@@ -22754,7 +22754,7 @@
       </c>
       <c r="D199" s="30" t="inlineStr">
         <is>
-          <t>HAZRATBAL ↔ LD</t>
+          <t>Hazratbal to LD</t>
         </is>
       </c>
       <c r="E199" s="29" t="inlineStr">
@@ -22864,7 +22864,7 @@
       </c>
       <c r="D200" s="56" t="inlineStr">
         <is>
-          <t>NARBAL ↔ JEHANGIR CHOWK</t>
+          <t>Narbal to Jehangir Chowk</t>
         </is>
       </c>
       <c r="E200" s="55" t="inlineStr">
@@ -22970,7 +22970,7 @@
       </c>
       <c r="D201" s="30" t="inlineStr">
         <is>
-          <t>HAZRATBAL ↔ LD</t>
+          <t>Hazratbal to LD</t>
         </is>
       </c>
       <c r="E201" s="29" t="inlineStr">
@@ -23080,7 +23080,7 @@
       </c>
       <c r="D202" s="30" t="inlineStr">
         <is>
-          <t>HAZRATBAL ↔ LD</t>
+          <t>Hazratbal to LD</t>
         </is>
       </c>
       <c r="E202" s="29" t="inlineStr">
@@ -23190,7 +23190,7 @@
       </c>
       <c r="D203" s="30" t="inlineStr">
         <is>
-          <t>SOURA ↔ PARIMPORA</t>
+          <t>Soura to Parimpora</t>
         </is>
       </c>
       <c r="E203" s="29" t="inlineStr">
@@ -23300,7 +23300,7 @@
       </c>
       <c r="D204" s="47" t="inlineStr">
         <is>
-          <t>SOURA ↔ JEHANGIR CHOWK</t>
+          <t>Soura to Jehangir Chowk</t>
         </is>
       </c>
       <c r="E204" s="46" t="inlineStr">
@@ -23406,7 +23406,7 @@
       </c>
       <c r="D205" s="52" t="inlineStr">
         <is>
-          <t>JEHANGIR CHOWK ↔ BUDGAM</t>
+          <t>Jehangir Chowk to Budgam</t>
         </is>
       </c>
       <c r="E205" s="51" t="inlineStr">
@@ -23512,7 +23512,7 @@
       </c>
       <c r="D206" s="56" t="inlineStr">
         <is>
-          <t>NARBAL ↔ JEHANGIR CHOWK</t>
+          <t>Narbal to Jehangir Chowk</t>
         </is>
       </c>
       <c r="E206" s="55" t="inlineStr">
@@ -23618,7 +23618,7 @@
       </c>
       <c r="D207" s="30" t="inlineStr">
         <is>
-          <t>HAZRATBAL ↔ LD</t>
+          <t>Hazratbal to LD</t>
         </is>
       </c>
       <c r="E207" s="29" t="inlineStr">
@@ -23728,7 +23728,7 @@
       </c>
       <c r="D208" s="43" t="inlineStr">
         <is>
-          <t>LAWAYPORA ↔ JEHANGIR CHOWK</t>
+          <t>Lawaypora to Jehangir Chowk</t>
         </is>
       </c>
       <c r="E208" s="42" t="inlineStr">
@@ -23838,7 +23838,7 @@
       </c>
       <c r="D209" s="30" t="inlineStr">
         <is>
-          <t>JEHANGIR CHOWK ↔ BEMINA</t>
+          <t>Jehangir Chowk to Bemina</t>
         </is>
       </c>
       <c r="E209" s="29" t="inlineStr">
@@ -23948,7 +23948,7 @@
       </c>
       <c r="D210" s="43" t="inlineStr">
         <is>
-          <t>RANGPORA ↔ LALCHOWK</t>
+          <t>Rangpora to Lalchowk</t>
         </is>
       </c>
       <c r="E210" s="42" t="inlineStr">
@@ -24058,7 +24058,7 @@
       </c>
       <c r="D211" s="43" t="inlineStr">
         <is>
-          <t>RANGPORA ↔ LALCHOWK</t>
+          <t>Rangpora to Lalchowk</t>
         </is>
       </c>
       <c r="E211" s="42" t="inlineStr">
@@ -24168,7 +24168,7 @@
       </c>
       <c r="D212" s="43" t="inlineStr">
         <is>
-          <t>RANGPORA ↔ LALCHOWK</t>
+          <t>Rangpora to Lalchowk</t>
         </is>
       </c>
       <c r="E212" s="42" t="inlineStr">
@@ -24278,7 +24278,7 @@
       </c>
       <c r="D213" s="30" t="inlineStr">
         <is>
-          <t>JEHANGIR CHOWK ↔ BEMINA</t>
+          <t>Jehangir Chowk to Bemina</t>
         </is>
       </c>
       <c r="E213" s="29" t="inlineStr">
@@ -24388,7 +24388,7 @@
       </c>
       <c r="D214" s="47" t="inlineStr">
         <is>
-          <t>SOURA ↔ JEHANGIR CHOWK</t>
+          <t>Soura to Jehangir Chowk</t>
         </is>
       </c>
       <c r="E214" s="46" t="inlineStr">
@@ -24494,7 +24494,7 @@
       </c>
       <c r="D215" s="37" t="inlineStr">
         <is>
-          <t>MALBAGH ↔ LD</t>
+          <t>Malbagh to LD</t>
         </is>
       </c>
       <c r="E215" s="36" t="inlineStr">
@@ -24600,7 +24600,7 @@
       </c>
       <c r="D216" s="30" t="inlineStr">
         <is>
-          <t>HAZRATBAL ↔ LD</t>
+          <t>Hazratbal to LD</t>
         </is>
       </c>
       <c r="E216" s="29" t="inlineStr">
@@ -24710,7 +24710,7 @@
       </c>
       <c r="D217" s="30" t="inlineStr">
         <is>
-          <t>JEHANGIR CHOWK ↔ BEMINA</t>
+          <t>Jehangir Chowk to Bemina</t>
         </is>
       </c>
       <c r="E217" s="29" t="inlineStr">
@@ -24820,7 +24820,7 @@
       </c>
       <c r="D218" s="56" t="inlineStr">
         <is>
-          <t>JEHANGIR CHOWK ↔ BUDGAM</t>
+          <t>Jehangir Chowk to Budgam</t>
         </is>
       </c>
       <c r="E218" s="55" t="inlineStr">
@@ -24926,7 +24926,7 @@
       </c>
       <c r="D219" s="43" t="inlineStr">
         <is>
-          <t>RANGPORA ↔ LALCHOWK</t>
+          <t>Rangpora to Lalchowk</t>
         </is>
       </c>
       <c r="E219" s="42" t="inlineStr">
@@ -25036,7 +25036,7 @@
       </c>
       <c r="D220" s="43" t="inlineStr">
         <is>
-          <t>RANGPORA ↔ LALCHOWK</t>
+          <t>Rangpora to Lalchowk</t>
         </is>
       </c>
       <c r="E220" s="42" t="inlineStr">
@@ -25146,7 +25146,7 @@
       </c>
       <c r="D221" s="37" t="inlineStr">
         <is>
-          <t>SOURA ↔ JEHANGIR CHOWK</t>
+          <t>Soura to Jehangir Chowk</t>
         </is>
       </c>
       <c r="E221" s="36" t="inlineStr">
@@ -25252,7 +25252,7 @@
       </c>
       <c r="D222" s="30" t="inlineStr">
         <is>
-          <t>HAZRATBAL ↔ LD</t>
+          <t>Hazratbal to LD</t>
         </is>
       </c>
       <c r="E222" s="29" t="inlineStr">
@@ -25362,7 +25362,7 @@
       </c>
       <c r="D223" s="37" t="inlineStr">
         <is>
-          <t>LALBAZAR ↔ LD</t>
+          <t>Lalbazar to LD</t>
         </is>
       </c>
       <c r="E223" s="36" t="inlineStr">
@@ -25468,7 +25468,7 @@
       </c>
       <c r="D224" s="47" t="inlineStr">
         <is>
-          <t>JEHANGIR CHOWK ↔ PANZINARA</t>
+          <t>Jehangir Chowk to Panzinara</t>
         </is>
       </c>
       <c r="E224" s="46" t="inlineStr">
@@ -25574,7 +25574,7 @@
       </c>
       <c r="D225" s="37" t="inlineStr">
         <is>
-          <t>LALBAZAR ↔ LD</t>
+          <t>Lalbazar to LD</t>
         </is>
       </c>
       <c r="E225" s="36" t="inlineStr">
@@ -25680,7 +25680,7 @@
       </c>
       <c r="D226" s="30" t="inlineStr">
         <is>
-          <t>HAZRATBAL ↔ LD</t>
+          <t>Hazratbal to LD</t>
         </is>
       </c>
       <c r="E226" s="29" t="inlineStr">
@@ -25790,7 +25790,7 @@
       </c>
       <c r="D227" s="30" t="inlineStr">
         <is>
-          <t>HAZRATBAL ↔ LD</t>
+          <t>Hazratbal to LD</t>
         </is>
       </c>
       <c r="E227" s="29" t="inlineStr">
@@ -25900,7 +25900,7 @@
       </c>
       <c r="D228" s="30" t="inlineStr">
         <is>
-          <t>HAZRATBAL ↔ LD</t>
+          <t>Hazratbal to LD</t>
         </is>
       </c>
       <c r="E228" s="29" t="inlineStr">
@@ -26010,7 +26010,7 @@
       </c>
       <c r="D229" s="30" t="inlineStr">
         <is>
-          <t>HAZRATBAL ↔ LD</t>
+          <t>Hazratbal to LD</t>
         </is>
       </c>
       <c r="E229" s="29" t="inlineStr">
@@ -26120,7 +26120,7 @@
       </c>
       <c r="D230" s="47" t="inlineStr">
         <is>
-          <t>SOURA ↔ RAILWAY STATION</t>
+          <t>Soura to Railway Station</t>
         </is>
       </c>
       <c r="E230" s="46" t="inlineStr">
@@ -26226,7 +26226,7 @@
       </c>
       <c r="D231" s="37" t="inlineStr">
         <is>
-          <t>SOURA ↔ JEHANGIR CHOWK</t>
+          <t>Soura to Jehangir Chowk</t>
         </is>
       </c>
       <c r="E231" s="36" t="inlineStr">
@@ -26332,7 +26332,7 @@
       </c>
       <c r="D232" s="47" t="inlineStr">
         <is>
-          <t>SOURA ↔ JEHANGIR CHOWK</t>
+          <t>Soura to Jehangir Chowk</t>
         </is>
       </c>
       <c r="E232" s="46" t="inlineStr">
@@ -26438,7 +26438,7 @@
       </c>
       <c r="D233" s="52" t="inlineStr">
         <is>
-          <t>NARBAL ↔ JEHANGIR CHOWK</t>
+          <t>Narbal to Jehangir Chowk</t>
         </is>
       </c>
       <c r="E233" s="51" t="inlineStr">
@@ -26544,7 +26544,7 @@
       </c>
       <c r="D234" s="47" t="inlineStr">
         <is>
-          <t>LALBAZAR ↔ LALCHOWK</t>
+          <t>Lalbazar to Lalchowk</t>
         </is>
       </c>
       <c r="E234" s="46" t="inlineStr">
@@ -26650,7 +26650,7 @@
       </c>
       <c r="D235" s="30" t="inlineStr">
         <is>
-          <t>HAZRATBAL ↔ LD</t>
+          <t>Hazratbal to LD</t>
         </is>
       </c>
       <c r="E235" s="29" t="inlineStr">
@@ -26760,7 +26760,7 @@
       </c>
       <c r="D236" s="47" t="inlineStr">
         <is>
-          <t>SOURA ↔ JEHANGIR CHOWK</t>
+          <t>Soura to Jehangir Chowk</t>
         </is>
       </c>
       <c r="E236" s="46" t="inlineStr">
@@ -26866,7 +26866,7 @@
       </c>
       <c r="D237" s="30" t="inlineStr">
         <is>
-          <t>SOURA ↔ LD</t>
+          <t>Soura to LD</t>
         </is>
       </c>
       <c r="E237" s="29" t="inlineStr">
@@ -26976,7 +26976,7 @@
       </c>
       <c r="D238" s="30" t="inlineStr">
         <is>
-          <t>SOURA ↔ HAZRATBAL</t>
+          <t>Soura to Hazratbal</t>
         </is>
       </c>
       <c r="E238" s="29" t="inlineStr">
@@ -27086,7 +27086,7 @@
       </c>
       <c r="D239" s="30" t="inlineStr">
         <is>
-          <t>SOURA ↔ HAZRATBAL</t>
+          <t>Soura to Hazratbal</t>
         </is>
       </c>
       <c r="E239" s="29" t="inlineStr">
@@ -27196,7 +27196,7 @@
       </c>
       <c r="D240" s="47" t="inlineStr">
         <is>
-          <t>SOURA ↔ RAILWAY STATION</t>
+          <t>Soura to Railway Station</t>
         </is>
       </c>
       <c r="E240" s="46" t="inlineStr">
@@ -27302,7 +27302,7 @@
       </c>
       <c r="D241" s="30" t="inlineStr">
         <is>
-          <t>SOURA ↔ LD</t>
+          <t>Soura to LD</t>
         </is>
       </c>
       <c r="E241" s="29" t="inlineStr">
@@ -27412,7 +27412,7 @@
       </c>
       <c r="D242" s="30" t="inlineStr">
         <is>
-          <t>HAZRATBAL ↔ LD</t>
+          <t>Hazratbal to LD</t>
         </is>
       </c>
       <c r="E242" s="29" t="inlineStr">
@@ -27522,7 +27522,7 @@
       </c>
       <c r="D243" s="30" t="inlineStr">
         <is>
-          <t>SOURA ↔ LD</t>
+          <t>Soura to LD</t>
         </is>
       </c>
       <c r="E243" s="29" t="inlineStr">
@@ -27632,7 +27632,7 @@
       </c>
       <c r="D244" s="30" t="inlineStr">
         <is>
-          <t>SOURA ↔ HAZRATBAL</t>
+          <t>Soura to Hazratbal</t>
         </is>
       </c>
       <c r="E244" s="29" t="inlineStr">
@@ -27742,7 +27742,7 @@
       </c>
       <c r="D245" s="37" t="inlineStr">
         <is>
-          <t>MA ROAD ↔ SAFAKADAL</t>
+          <t>Ma Road to Safakadal</t>
         </is>
       </c>
       <c r="E245" s="36" t="inlineStr">
@@ -27848,7 +27848,7 @@
       </c>
       <c r="D246" s="30" t="inlineStr">
         <is>
-          <t>SOURA ↔ LD</t>
+          <t>Soura to LD</t>
         </is>
       </c>
       <c r="E246" s="29" t="inlineStr">
@@ -27958,7 +27958,7 @@
       </c>
       <c r="D247" s="30" t="inlineStr">
         <is>
-          <t>SOURA ↔ LD</t>
+          <t>Soura to LD</t>
         </is>
       </c>
       <c r="E247" s="29" t="inlineStr">
@@ -28068,7 +28068,7 @@
       </c>
       <c r="D248" s="30" t="inlineStr">
         <is>
-          <t>BAGHAT SHORA ↔ LALCHOWK</t>
+          <t>Baghat Shora to Lalchowk</t>
         </is>
       </c>
       <c r="E248" s="29" t="inlineStr">
@@ -28178,7 +28178,7 @@
       </c>
       <c r="D249" s="37" t="inlineStr">
         <is>
-          <t>CHANAPORA ↔ SOURA</t>
+          <t>Chanapora to Soura</t>
         </is>
       </c>
       <c r="E249" s="36" t="inlineStr">
@@ -28284,7 +28284,7 @@
       </c>
       <c r="D250" s="30" t="inlineStr">
         <is>
-          <t>SOURA ↔ LD</t>
+          <t>Soura to LD</t>
         </is>
       </c>
       <c r="E250" s="29" t="inlineStr">
@@ -28394,7 +28394,7 @@
       </c>
       <c r="D251" s="30" t="inlineStr">
         <is>
-          <t>SOURA ↔ LD</t>
+          <t>Soura to LD</t>
         </is>
       </c>
       <c r="E251" s="29" t="inlineStr">
@@ -28504,7 +28504,7 @@
       </c>
       <c r="D252" s="47" t="inlineStr">
         <is>
-          <t>SOURA ↔ JEHANGIR CHOWK</t>
+          <t>Soura to Jehangir Chowk</t>
         </is>
       </c>
       <c r="E252" s="46" t="inlineStr">
@@ -28610,7 +28610,7 @@
       </c>
       <c r="D253" s="30" t="inlineStr">
         <is>
-          <t>SOURA ↔ LD</t>
+          <t>Soura to LD</t>
         </is>
       </c>
       <c r="E253" s="29" t="inlineStr">
@@ -28720,7 +28720,7 @@
       </c>
       <c r="D254" s="30" t="inlineStr">
         <is>
-          <t>BAGHAT SHORA ↔ LALCHOWK</t>
+          <t>Baghat Shora to Lalchowk</t>
         </is>
       </c>
       <c r="E254" s="29" t="inlineStr">
@@ -28830,7 +28830,7 @@
       </c>
       <c r="D255" s="30" t="inlineStr">
         <is>
-          <t>SOURA ↔ LALCHOWK</t>
+          <t>Soura to Lalchowk</t>
         </is>
       </c>
       <c r="E255" s="29" t="inlineStr">
@@ -28940,7 +28940,7 @@
       </c>
       <c r="D256" s="30" t="inlineStr">
         <is>
-          <t>HAZRATBAL ↔ LD</t>
+          <t>Hazratbal to LD</t>
         </is>
       </c>
       <c r="E256" s="29" t="inlineStr">
@@ -29050,7 +29050,7 @@
       </c>
       <c r="D257" s="30" t="inlineStr">
         <is>
-          <t>BAGHAT SHORA ↔ LALCHOWK</t>
+          <t>Baghat Shora to Lalchowk</t>
         </is>
       </c>
       <c r="E257" s="29" t="inlineStr">
@@ -29160,7 +29160,7 @@
       </c>
       <c r="D258" s="30" t="inlineStr">
         <is>
-          <t>SOURA ↔ LALCHOWK</t>
+          <t>Soura to Lalchowk</t>
         </is>
       </c>
       <c r="E258" s="29" t="inlineStr">
@@ -29270,7 +29270,7 @@
       </c>
       <c r="D259" s="43" t="inlineStr">
         <is>
-          <t>LAWAYPORA ↔ JEHANGIR CHOWK</t>
+          <t>Lawaypora to Jehangir Chowk</t>
         </is>
       </c>
       <c r="E259" s="42" t="inlineStr">
@@ -29380,7 +29380,7 @@
       </c>
       <c r="D260" s="30" t="inlineStr">
         <is>
-          <t>SOURA ↔ LD</t>
+          <t>Soura to LD</t>
         </is>
       </c>
       <c r="E260" s="29" t="inlineStr">
@@ -29490,7 +29490,7 @@
       </c>
       <c r="D261" s="37" t="inlineStr">
         <is>
-          <t>SOURA ↔ GANDERBAL</t>
+          <t>Soura to Ganderbal</t>
         </is>
       </c>
       <c r="E261" s="36" t="inlineStr">
@@ -29596,7 +29596,7 @@
       </c>
       <c r="D262" s="47" t="inlineStr">
         <is>
-          <t>SOURA ↔ GANDERBAL</t>
+          <t>Soura to Ganderbal</t>
         </is>
       </c>
       <c r="E262" s="46" t="inlineStr">
@@ -29702,7 +29702,7 @@
       </c>
       <c r="D263" s="30" t="inlineStr">
         <is>
-          <t>SOURA ↔ HAZRATBAL</t>
+          <t>Soura to Hazratbal</t>
         </is>
       </c>
       <c r="E263" s="29" t="inlineStr">
@@ -29812,7 +29812,7 @@
       </c>
       <c r="D264" s="47" t="inlineStr">
         <is>
-          <t>JEHANGIR CHOWK ↔ HMT</t>
+          <t>Jehangir Chowk to HMT</t>
         </is>
       </c>
       <c r="E264" s="46" t="inlineStr">
@@ -29918,7 +29918,7 @@
       </c>
       <c r="D265" s="37" t="inlineStr">
         <is>
-          <t>MALBAGH ↔ LD</t>
+          <t>Malbagh to LD</t>
         </is>
       </c>
       <c r="E265" s="36" t="inlineStr">
@@ -30024,7 +30024,7 @@
       </c>
       <c r="D266" s="56" t="inlineStr">
         <is>
-          <t>JEHANGIR CHOWK ↔ JVC</t>
+          <t>Jehangir Chowk to JVC</t>
         </is>
       </c>
       <c r="E266" s="55" t="inlineStr">
@@ -30130,7 +30130,7 @@
       </c>
       <c r="D267" s="37" t="inlineStr">
         <is>
-          <t>MA ROAD ↔ PARIMPORA</t>
+          <t>Ma Road to Parimpora</t>
         </is>
       </c>
       <c r="E267" s="36" t="inlineStr">
@@ -30236,7 +30236,7 @@
       </c>
       <c r="D268" s="47" t="inlineStr">
         <is>
-          <t>TRC ↔ HAZRATBAL</t>
+          <t>TRC to Hazratbal</t>
         </is>
       </c>
       <c r="E268" s="46" t="inlineStr">
@@ -30342,7 +30342,7 @@
       </c>
       <c r="D269" s="37" t="inlineStr">
         <is>
-          <t>TRC ↔ HAZRATBAL</t>
+          <t>TRC to Hazratbal</t>
         </is>
       </c>
       <c r="E269" s="36" t="inlineStr">
@@ -30448,7 +30448,7 @@
       </c>
       <c r="D270" s="30" t="inlineStr">
         <is>
-          <t>SOURA ↔ HAZRATBAL</t>
+          <t>Soura to Hazratbal</t>
         </is>
       </c>
       <c r="E270" s="29" t="inlineStr">
@@ -30558,7 +30558,7 @@
       </c>
       <c r="D271" s="30" t="inlineStr">
         <is>
-          <t>SOURA ↔ HAZRATBAL</t>
+          <t>Soura to Hazratbal</t>
         </is>
       </c>
       <c r="E271" s="29" t="inlineStr">
@@ -30668,7 +30668,7 @@
       </c>
       <c r="D272" s="30" t="inlineStr">
         <is>
-          <t>SOURA ↔ HAZRATBAL</t>
+          <t>Soura to Hazratbal</t>
         </is>
       </c>
       <c r="E272" s="29" t="inlineStr">
@@ -30778,7 +30778,7 @@
       </c>
       <c r="D273" s="30" t="inlineStr">
         <is>
-          <t>SOURA ↔ LD</t>
+          <t>Soura to LD</t>
         </is>
       </c>
       <c r="E273" s="29" t="inlineStr">
@@ -30888,7 +30888,7 @@
       </c>
       <c r="D274" s="30" t="inlineStr">
         <is>
-          <t>SOURA ↔ LD</t>
+          <t>Soura to LD</t>
         </is>
       </c>
       <c r="E274" s="29" t="inlineStr">
@@ -30998,7 +30998,7 @@
       </c>
       <c r="D275" s="43" t="inlineStr">
         <is>
-          <t>SAFAKADAL ↔ JEHANGIR CHOWK</t>
+          <t>Safakadal to Jehangir Chowk</t>
         </is>
       </c>
       <c r="E275" s="42" t="inlineStr">
@@ -31108,7 +31108,7 @@
       </c>
       <c r="D276" s="47" t="inlineStr">
         <is>
-          <t>JEHANGIR CHOWK ↔ HMT</t>
+          <t>Jehangir Chowk to HMT</t>
         </is>
       </c>
       <c r="E276" s="46" t="inlineStr">
@@ -31214,7 +31214,7 @@
       </c>
       <c r="D277" s="30" t="inlineStr">
         <is>
-          <t>SOURA ↔ LD</t>
+          <t>Soura to LD</t>
         </is>
       </c>
       <c r="E277" s="29" t="inlineStr">
@@ -31324,7 +31324,7 @@
       </c>
       <c r="D278" s="56" t="inlineStr">
         <is>
-          <t>JEHANGIR CHOWK ↔ JVC</t>
+          <t>Jehangir Chowk to JVC</t>
         </is>
       </c>
       <c r="E278" s="55" t="inlineStr">
@@ -31430,7 +31430,7 @@
       </c>
       <c r="D279" s="30" t="inlineStr">
         <is>
-          <t>SOURA ↔ LD</t>
+          <t>Soura to LD</t>
         </is>
       </c>
       <c r="E279" s="29" t="inlineStr">
@@ -31540,7 +31540,7 @@
       </c>
       <c r="D280" s="30" t="inlineStr">
         <is>
-          <t>SOURA ↔ LD</t>
+          <t>Soura to LD</t>
         </is>
       </c>
       <c r="E280" s="29" t="inlineStr">
@@ -31650,7 +31650,7 @@
       </c>
       <c r="D281" s="43" t="inlineStr">
         <is>
-          <t>PARIMPORA ↔ JAWAHIRNAGAR</t>
+          <t>Parimpora to Jawahirnagar</t>
         </is>
       </c>
       <c r="E281" s="42" t="inlineStr">
@@ -31760,7 +31760,7 @@
       </c>
       <c r="D282" s="43" t="inlineStr">
         <is>
-          <t>SAFAKADAL ↔ JEHANGIR CHOWK</t>
+          <t>Safakadal to Jehangir Chowk</t>
         </is>
       </c>
       <c r="E282" s="42" t="inlineStr">
@@ -31870,7 +31870,7 @@
       </c>
       <c r="D283" s="37" t="inlineStr">
         <is>
-          <t>SRINAGAR to SHANGLIPORA</t>
+          <t>Srinagar to Shanglipora</t>
         </is>
       </c>
       <c r="E283" s="36" t="inlineStr">
@@ -31976,7 +31976,7 @@
       </c>
       <c r="D284" s="47" t="inlineStr">
         <is>
-          <t>SRINAGAR to CHEWDARA</t>
+          <t>Srinagar to Chewdara</t>
         </is>
       </c>
       <c r="E284" s="46" t="inlineStr">
@@ -32082,7 +32082,7 @@
       </c>
       <c r="D285" s="52" t="inlineStr">
         <is>
-          <t>SRINAGAR to CHOWKIBAL</t>
+          <t>Srinagar to Chowkibal</t>
         </is>
       </c>
       <c r="E285" s="51" t="inlineStr">
@@ -32188,7 +32188,7 @@
       </c>
       <c r="D286" s="56" t="inlineStr">
         <is>
-          <t>SRINAGAR to SAFAPORA SUMBAL</t>
+          <t>Srinagar to Safapora Sumbal</t>
         </is>
       </c>
       <c r="E286" s="55" t="inlineStr">
@@ -32294,7 +32294,7 @@
       </c>
       <c r="D287" s="37" t="inlineStr">
         <is>
-          <t>SRINAGAR to URI BARAMULLA</t>
+          <t>Srinagar to URI Baramulla</t>
         </is>
       </c>
       <c r="E287" s="36" t="inlineStr">
@@ -32400,7 +32400,7 @@
       </c>
       <c r="D288" s="47" t="inlineStr">
         <is>
-          <t>BANDIPORA to SRINAGAR</t>
+          <t>Bandipora to Srinagar</t>
         </is>
       </c>
       <c r="E288" s="46" t="inlineStr">
@@ -32506,7 +32506,7 @@
       </c>
       <c r="D289" s="37" t="inlineStr">
         <is>
-          <t>BANDIPORA to SRINAGAR</t>
+          <t>Bandipora to Srinagar</t>
         </is>
       </c>
       <c r="E289" s="36" t="inlineStr">
@@ -32612,7 +32612,7 @@
       </c>
       <c r="D290" s="47" t="inlineStr">
         <is>
-          <t>BANDIPORA to SRINAGAR</t>
+          <t>Bandipora to Srinagar</t>
         </is>
       </c>
       <c r="E290" s="46" t="inlineStr">
@@ -32718,7 +32718,7 @@
       </c>
       <c r="D291" s="37" t="inlineStr">
         <is>
-          <t>SRINAGAR to BANDIPORA</t>
+          <t>Srinagar to Bandipora</t>
         </is>
       </c>
       <c r="E291" s="36" t="inlineStr">
@@ -32824,7 +32824,7 @@
       </c>
       <c r="D292" s="47" t="inlineStr">
         <is>
-          <t>BANDIPORA to BARAMULLA</t>
+          <t>Bandipora to Baramulla</t>
         </is>
       </c>
       <c r="E292" s="46" t="inlineStr">
@@ -32930,7 +32930,7 @@
       </c>
       <c r="D293" s="37" t="inlineStr">
         <is>
-          <t>SRINAGAR to ZALOORA</t>
+          <t>Srinagar to Zaloora</t>
         </is>
       </c>
       <c r="E293" s="36" t="inlineStr">
@@ -33036,7 +33036,7 @@
       </c>
       <c r="D294" s="47" t="inlineStr">
         <is>
-          <t>SRINAGAR to BARAMULLA</t>
+          <t>Srinagar to Baramulla</t>
         </is>
       </c>
       <c r="E294" s="46" t="inlineStr">
@@ -33142,7 +33142,7 @@
       </c>
       <c r="D295" s="37" t="inlineStr">
         <is>
-          <t>KAMALKOTE to BARAMULLA</t>
+          <t>Kamalkote to Baramulla</t>
         </is>
       </c>
       <c r="E295" s="36" t="inlineStr">
@@ -33248,7 +33248,7 @@
       </c>
       <c r="D296" s="47" t="inlineStr">
         <is>
-          <t>GARKOTE to BARAMULLA</t>
+          <t>Garkote to Baramulla</t>
         </is>
       </c>
       <c r="E296" s="46" t="inlineStr">
@@ -33354,7 +33354,7 @@
       </c>
       <c r="D297" s="37" t="inlineStr">
         <is>
-          <t>NAMBIA to BARAMULLA</t>
+          <t>Nambia to Baramulla</t>
         </is>
       </c>
       <c r="E297" s="36" t="inlineStr">
@@ -33460,7 +33460,7 @@
       </c>
       <c r="D298" s="47" t="inlineStr">
         <is>
-          <t>BARAMULA to KUPWRA</t>
+          <t>Baramula to Kupwra</t>
         </is>
       </c>
       <c r="E298" s="46" t="inlineStr">
@@ -33566,7 +33566,7 @@
       </c>
       <c r="D299" s="37" t="inlineStr">
         <is>
-          <t>HARMAN to SRINAGAR</t>
+          <t>Harman to Srinagar</t>
         </is>
       </c>
       <c r="E299" s="36" t="inlineStr">
@@ -33672,7 +33672,7 @@
       </c>
       <c r="D300" s="47" t="inlineStr">
         <is>
-          <t>SRINAGAR to BY PASS</t>
+          <t>Srinagar to By Pass</t>
         </is>
       </c>
       <c r="E300" s="46" t="inlineStr">
@@ -33778,7 +33778,7 @@
       </c>
       <c r="D301" s="37" t="inlineStr">
         <is>
-          <t>SRINAGAR to BYPASS</t>
+          <t>Srinagar to Bypass</t>
         </is>
       </c>
       <c r="E301" s="36" t="inlineStr">
@@ -33884,7 +33884,7 @@
       </c>
       <c r="D302" s="47" t="inlineStr">
         <is>
-          <t>SRINAGAR to GULABAGH</t>
+          <t>Srinagar to Gulabagh</t>
         </is>
       </c>
       <c r="E302" s="46" t="inlineStr">
@@ -33990,7 +33990,7 @@
       </c>
       <c r="D303" s="37" t="inlineStr">
         <is>
-          <t>SRINAGAR to BYPASS</t>
+          <t>Srinagar to Bypass</t>
         </is>
       </c>
       <c r="E303" s="36" t="inlineStr">
@@ -34096,7 +34096,7 @@
       </c>
       <c r="D304" s="47" t="inlineStr">
         <is>
-          <t>SRINAGAR to BYPASS</t>
+          <t>Srinagar to Bypass</t>
         </is>
       </c>
       <c r="E304" s="46" t="inlineStr">
@@ -34202,7 +34202,7 @@
       </c>
       <c r="D305" s="37" t="inlineStr">
         <is>
-          <t>SRINAGAR to BUCHPORA</t>
+          <t>Srinagar to Buchpora</t>
         </is>
       </c>
       <c r="E305" s="36" t="inlineStr">
@@ -34308,7 +34308,7 @@
       </c>
       <c r="D306" s="47" t="inlineStr">
         <is>
-          <t>SRINAGAR to BYPASS</t>
+          <t>Srinagar to Bypass</t>
         </is>
       </c>
       <c r="E306" s="46" t="inlineStr">
@@ -34414,7 +34414,7 @@
       </c>
       <c r="D307" s="37" t="inlineStr">
         <is>
-          <t>SRINAGAR to HARWAN</t>
+          <t>Srinagar to Harwan</t>
         </is>
       </c>
       <c r="E307" s="36" t="inlineStr">
@@ -34520,7 +34520,7 @@
       </c>
       <c r="D308" s="47" t="inlineStr">
         <is>
-          <t>SRINAGAR to HARWAN</t>
+          <t>Srinagar to Harwan</t>
         </is>
       </c>
       <c r="E308" s="46" t="inlineStr">
@@ -34626,7 +34626,7 @@
       </c>
       <c r="D309" s="37" t="inlineStr">
         <is>
-          <t>SRINAGAR to GULABAGH</t>
+          <t>Srinagar to Gulabagh</t>
         </is>
       </c>
       <c r="E309" s="36" t="inlineStr">
@@ -34732,7 +34732,7 @@
       </c>
       <c r="D310" s="47" t="inlineStr">
         <is>
-          <t>SRINAGAR to BYPASS</t>
+          <t>Srinagar to Bypass</t>
         </is>
       </c>
       <c r="E310" s="46" t="inlineStr">
@@ -34838,7 +34838,7 @@
       </c>
       <c r="D311" s="37" t="inlineStr">
         <is>
-          <t>SRINAGAR to GANDERBAL</t>
+          <t>Srinagar to Ganderbal</t>
         </is>
       </c>
       <c r="E311" s="36" t="inlineStr">
@@ -34944,7 +34944,7 @@
       </c>
       <c r="D312" s="47" t="inlineStr">
         <is>
-          <t>SRINAGAR to BYPASS</t>
+          <t>Srinagar to Bypass</t>
         </is>
       </c>
       <c r="E312" s="46" t="inlineStr">
@@ -35050,7 +35050,7 @@
       </c>
       <c r="D313" s="37" t="inlineStr">
         <is>
-          <t>SRINAGAR to HARWAN</t>
+          <t>Srinagar to Harwan</t>
         </is>
       </c>
       <c r="E313" s="36" t="inlineStr">
@@ -36958,7 +36958,7 @@
       </c>
       <c r="D331" s="37" t="inlineStr">
         <is>
-          <t>JKPDC Jehangir Chowk to Wadwan</t>
+          <t>Jkpdc Jehangir Chowk to Wadwan</t>
         </is>
       </c>
       <c r="E331" s="36" t="inlineStr">
@@ -38230,7 +38230,7 @@
       </c>
       <c r="D343" s="52" t="inlineStr">
         <is>
-          <t>Batamaloo to DC Office Budgam</t>
+          <t>Batamaloo to Dc Office Budgam</t>
         </is>
       </c>
       <c r="E343" s="51" t="inlineStr">
@@ -40804,7 +40804,7 @@
       </c>
       <c r="C5" s="18" t="inlineStr">
         <is>
-          <t>SOURA ↔ HAZRATBAL</t>
+          <t>Soura to Hazratbal</t>
         </is>
       </c>
       <c r="D5" s="67" t="n">
@@ -40823,7 +40823,7 @@
       </c>
       <c r="C6" s="20" t="inlineStr">
         <is>
-          <t>NARBAL ↔ JEHANGIR CHOWK</t>
+          <t>Narbal to Jehangir Chowk</t>
         </is>
       </c>
       <c r="D6" s="70" t="n">
@@ -40846,7 +40846,7 @@
       </c>
       <c r="C7" s="18" t="inlineStr">
         <is>
-          <t>NARBAL ↔ JEHANGIR CHOWK</t>
+          <t>Narbal to Jehangir Chowk</t>
         </is>
       </c>
       <c r="D7" s="67" t="n">
@@ -40869,7 +40869,7 @@
       </c>
       <c r="C8" s="20" t="inlineStr">
         <is>
-          <t>NARBAL ↔ JEHANGIR CHOWK</t>
+          <t>Narbal to Jehangir Chowk</t>
         </is>
       </c>
       <c r="D8" s="70" t="n">
@@ -40892,7 +40892,7 @@
       </c>
       <c r="C9" s="18" t="inlineStr">
         <is>
-          <t>HAZRATBAL ↔ BONE JOINT HOSPITAL BARZALLA</t>
+          <t>Hazratbal to Bone Joint Hospital Barzalla</t>
         </is>
       </c>
       <c r="D9" s="67" t="n">
@@ -40911,7 +40911,7 @@
       </c>
       <c r="C10" s="20" t="inlineStr">
         <is>
-          <t>PARIMPORA ↔ JAWAHAIRNAGAR</t>
+          <t>Parimpora to Jawahairnagar</t>
         </is>
       </c>
       <c r="D10" s="70" t="n">
@@ -40930,7 +40930,7 @@
       </c>
       <c r="C11" s="18" t="inlineStr">
         <is>
-          <t>NARBAL ↔ JEHANGIR CHOWK</t>
+          <t>Narbal to Jehangir Chowk</t>
         </is>
       </c>
       <c r="D11" s="67" t="n">
@@ -40953,7 +40953,7 @@
       </c>
       <c r="C12" s="20" t="inlineStr">
         <is>
-          <t>SOURA ↔ DALGATE</t>
+          <t>Soura to Dalgate</t>
         </is>
       </c>
       <c r="D12" s="70" t="n">
@@ -40972,7 +40972,7 @@
       </c>
       <c r="C13" s="18" t="inlineStr">
         <is>
-          <t>SOURA ↔ BATAMALLO</t>
+          <t>Soura to Batamallo</t>
         </is>
       </c>
       <c r="D13" s="67" t="n">
@@ -40995,7 +40995,7 @@
       </c>
       <c r="C14" s="20" t="inlineStr">
         <is>
-          <t>NARBAL ↔ JEHANGIR CHOWK</t>
+          <t>Narbal to Jehangir Chowk</t>
         </is>
       </c>
       <c r="D14" s="70" t="n">
@@ -41018,7 +41018,7 @@
       </c>
       <c r="C15" s="18" t="inlineStr">
         <is>
-          <t>NARBAL ↔ JEHANGIR CHOWK</t>
+          <t>Narbal to Jehangir Chowk</t>
         </is>
       </c>
       <c r="D15" s="67" t="n">
@@ -41041,7 +41041,7 @@
       </c>
       <c r="C16" s="20" t="inlineStr">
         <is>
-          <t>NARBAL ↔ JEHANGIR CHOWK</t>
+          <t>Narbal to Jehangir Chowk</t>
         </is>
       </c>
       <c r="D16" s="70" t="n">
@@ -41064,7 +41064,7 @@
       </c>
       <c r="C17" s="18" t="inlineStr">
         <is>
-          <t>NARBAL ↔ JEHANGIR CHOWK</t>
+          <t>Narbal to Jehangir Chowk</t>
         </is>
       </c>
       <c r="D17" s="67" t="n">
@@ -41087,7 +41087,7 @@
       </c>
       <c r="C18" s="20" t="inlineStr">
         <is>
-          <t>NARBAL ↔ JEHANGIR CHOWK</t>
+          <t>Narbal to Jehangir Chowk</t>
         </is>
       </c>
       <c r="D18" s="70" t="n">
@@ -41110,7 +41110,7 @@
       </c>
       <c r="C19" s="18" t="inlineStr">
         <is>
-          <t>SRINAGAR to CHOWKIBAL</t>
+          <t>Srinagar to Chowkibal</t>
         </is>
       </c>
       <c r="D19" s="67" t="n">
@@ -41133,7 +41133,7 @@
       </c>
       <c r="C20" s="20" t="inlineStr">
         <is>
-          <t>BANDIPORA to BARAMULLA</t>
+          <t>Bandipora to Baramulla</t>
         </is>
       </c>
       <c r="D20" s="70" t="n">
@@ -41156,7 +41156,7 @@
       </c>
       <c r="C21" s="18" t="inlineStr">
         <is>
-          <t>KAMALKOTE to BARAMULLA</t>
+          <t>Kamalkote to Baramulla</t>
         </is>
       </c>
       <c r="D21" s="67" t="n">
@@ -41179,7 +41179,7 @@
       </c>
       <c r="C22" s="20" t="inlineStr">
         <is>
-          <t>GARKOTE to BARAMULLA</t>
+          <t>Garkote to Baramulla</t>
         </is>
       </c>
       <c r="D22" s="70" t="n">
@@ -41202,7 +41202,7 @@
       </c>
       <c r="C23" s="18" t="inlineStr">
         <is>
-          <t>NAMBIA to BARAMULLA</t>
+          <t>Nambia to Baramulla</t>
         </is>
       </c>
       <c r="D23" s="67" t="n">
@@ -41616,7 +41616,7 @@
       </c>
       <c r="C41" s="18" t="inlineStr">
         <is>
-          <t>JKPDC Jehangir Chowk to Wadwan</t>
+          <t>Jkpdc Jehangir Chowk to Wadwan</t>
         </is>
       </c>
       <c r="D41" s="67" t="n">
@@ -41892,7 +41892,7 @@
       </c>
       <c r="C53" s="18" t="inlineStr">
         <is>
-          <t>Batamaloo to DC Office Budgam</t>
+          <t>Batamaloo to Dc Office Budgam</t>
         </is>
       </c>
       <c r="D53" s="67" t="n">
@@ -41970,7 +41970,7 @@
       </c>
       <c r="C5" s="18" t="inlineStr">
         <is>
-          <t>LAWAYPORA ↔ JEHANGIR CHOWK</t>
+          <t>Lawaypora to Jehangir Chowk</t>
         </is>
       </c>
       <c r="D5" s="67" t="n">
@@ -41993,7 +41993,7 @@
       </c>
       <c r="C6" s="20" t="inlineStr">
         <is>
-          <t>JEHANGIR CHOWK ↔ JVC</t>
+          <t>Jehangir Chowk to JVC</t>
         </is>
       </c>
       <c r="D6" s="70" t="n">
@@ -42016,7 +42016,7 @@
       </c>
       <c r="C7" s="18" t="inlineStr">
         <is>
-          <t>JEHANGIR CHOWK ↔ JVC</t>
+          <t>Jehangir Chowk to JVC</t>
         </is>
       </c>
       <c r="D7" s="67" t="n">
@@ -42039,7 +42039,7 @@
       </c>
       <c r="C8" s="20" t="inlineStr">
         <is>
-          <t>JEHANGIR CHOWK ↔ JVC</t>
+          <t>Jehangir Chowk to JVC</t>
         </is>
       </c>
       <c r="D8" s="70" t="n">
@@ -42062,7 +42062,7 @@
       </c>
       <c r="C9" s="18" t="inlineStr">
         <is>
-          <t>JEHANGIR CHOWK ↔ JVC</t>
+          <t>Jehangir Chowk to JVC</t>
         </is>
       </c>
       <c r="D9" s="67" t="n">
@@ -42085,7 +42085,7 @@
       </c>
       <c r="C10" s="20" t="inlineStr">
         <is>
-          <t>JEHANGIR CHOWK ↔ BUDGAM</t>
+          <t>Jehangir Chowk to Budgam</t>
         </is>
       </c>
       <c r="D10" s="70" t="n">
@@ -42108,7 +42108,7 @@
       </c>
       <c r="C11" s="18" t="inlineStr">
         <is>
-          <t>JEHANGIR CHOWK ↔ JVC</t>
+          <t>Jehangir Chowk to JVC</t>
         </is>
       </c>
       <c r="D11" s="67" t="n">
@@ -42131,7 +42131,7 @@
       </c>
       <c r="C12" s="20" t="inlineStr">
         <is>
-          <t>JEHANGIR CHOWK ↔ JVC</t>
+          <t>Jehangir Chowk to JVC</t>
         </is>
       </c>
       <c r="D12" s="70" t="n">
@@ -42154,7 +42154,7 @@
       </c>
       <c r="C13" s="18" t="inlineStr">
         <is>
-          <t>PARIMPORA ↔ RAWALPORA</t>
+          <t>Parimpora to Rawalpora</t>
         </is>
       </c>
       <c r="D13" s="67" t="n">
@@ -42177,7 +42177,7 @@
       </c>
       <c r="C14" s="20" t="inlineStr">
         <is>
-          <t>PARIMPORA ↔ RAWALPORA</t>
+          <t>Parimpora to Rawalpora</t>
         </is>
       </c>
       <c r="D14" s="70" t="n">
@@ -42200,7 +42200,7 @@
       </c>
       <c r="C15" s="18" t="inlineStr">
         <is>
-          <t>PARIMPORA ↔ RAWALPORA</t>
+          <t>Parimpora to Rawalpora</t>
         </is>
       </c>
       <c r="D15" s="67" t="n">
@@ -42223,7 +42223,7 @@
       </c>
       <c r="C16" s="20" t="inlineStr">
         <is>
-          <t>NARBAL ↔ JEHANGIR CHOWK</t>
+          <t>Narbal to Jehangir Chowk</t>
         </is>
       </c>
       <c r="D16" s="70" t="n">
@@ -42246,7 +42246,7 @@
       </c>
       <c r="C17" s="18" t="inlineStr">
         <is>
-          <t>SAFAKADAL ↔ JEHANGIR CHOWK</t>
+          <t>Safakadal to Jehangir Chowk</t>
         </is>
       </c>
       <c r="D17" s="67" t="n">
@@ -42269,7 +42269,7 @@
       </c>
       <c r="C18" s="20" t="inlineStr">
         <is>
-          <t>SAFAKADAL ↔ JEHANGIR CHOWK</t>
+          <t>Safakadal to Jehangir Chowk</t>
         </is>
       </c>
       <c r="D18" s="70" t="n">
@@ -42292,7 +42292,7 @@
       </c>
       <c r="C19" s="18" t="inlineStr">
         <is>
-          <t>SAFAKADAL ↔ JEHANGIR CHOWK</t>
+          <t>Safakadal to Jehangir Chowk</t>
         </is>
       </c>
       <c r="D19" s="67" t="n">
@@ -42315,7 +42315,7 @@
       </c>
       <c r="C20" s="20" t="inlineStr">
         <is>
-          <t>SAFAKADAL ↔ JEHANGIR CHOWK</t>
+          <t>Safakadal to Jehangir Chowk</t>
         </is>
       </c>
       <c r="D20" s="70" t="n">
@@ -42338,7 +42338,7 @@
       </c>
       <c r="C21" s="18" t="inlineStr">
         <is>
-          <t>QAMARWARI ↔ DALGATE</t>
+          <t>Qamarwari to Dalgate</t>
         </is>
       </c>
       <c r="D21" s="67" t="n">
@@ -42361,7 +42361,7 @@
       </c>
       <c r="C22" s="20" t="inlineStr">
         <is>
-          <t>QAMARWARI ↔ DALGATE</t>
+          <t>Qamarwari to Dalgate</t>
         </is>
       </c>
       <c r="D22" s="70" t="n">
@@ -42384,7 +42384,7 @@
       </c>
       <c r="C23" s="18" t="inlineStr">
         <is>
-          <t>PARIMPORA ↔ RAWALPORA</t>
+          <t>Parimpora to Rawalpora</t>
         </is>
       </c>
       <c r="D23" s="67" t="n">
@@ -42407,7 +42407,7 @@
       </c>
       <c r="C24" s="20" t="inlineStr">
         <is>
-          <t>SAFAKADAL ↔ JEHANGIR CHOWK</t>
+          <t>Safakadal to Jehangir Chowk</t>
         </is>
       </c>
       <c r="D24" s="70" t="n">
@@ -42430,7 +42430,7 @@
       </c>
       <c r="C25" s="18" t="inlineStr">
         <is>
-          <t>SAFAKADAL ↔ JEHANGIR CHOWK</t>
+          <t>Safakadal to Jehangir Chowk</t>
         </is>
       </c>
       <c r="D25" s="67" t="n">
@@ -42453,7 +42453,7 @@
       </c>
       <c r="C26" s="20" t="inlineStr">
         <is>
-          <t>SAFAKADAL ↔ JEHANGIR CHOWK</t>
+          <t>Safakadal to Jehangir Chowk</t>
         </is>
       </c>
       <c r="D26" s="70" t="n">
@@ -42476,7 +42476,7 @@
       </c>
       <c r="C27" s="18" t="inlineStr">
         <is>
-          <t>SAFAKADAL ↔ JEHANGIR CHOWK</t>
+          <t>Safakadal to Jehangir Chowk</t>
         </is>
       </c>
       <c r="D27" s="67" t="n">
@@ -42499,7 +42499,7 @@
       </c>
       <c r="C28" s="20" t="inlineStr">
         <is>
-          <t>SAFAKADAL ↔ JEHANGIR CHOWK</t>
+          <t>Safakadal to Jehangir Chowk</t>
         </is>
       </c>
       <c r="D28" s="70" t="n">
@@ -42522,7 +42522,7 @@
       </c>
       <c r="C29" s="18" t="inlineStr">
         <is>
-          <t>SAFAKADAL ↔ JEHANGIR CHOWK</t>
+          <t>Safakadal to Jehangir Chowk</t>
         </is>
       </c>
       <c r="D29" s="67" t="n">
@@ -42545,7 +42545,7 @@
       </c>
       <c r="C30" s="20" t="inlineStr">
         <is>
-          <t>PARIMPORA ↔ RAWALPORA</t>
+          <t>Parimpora to Rawalpora</t>
         </is>
       </c>
       <c r="D30" s="70" t="n">
@@ -42568,7 +42568,7 @@
       </c>
       <c r="C31" s="18" t="inlineStr">
         <is>
-          <t>JEHANGIR CHOWK ↔ JVC</t>
+          <t>Jehangir Chowk to JVC</t>
         </is>
       </c>
       <c r="D31" s="67" t="n">
@@ -42591,7 +42591,7 @@
       </c>
       <c r="C32" s="20" t="inlineStr">
         <is>
-          <t>JEHANGIR CHOWK ↔ BUDGAM</t>
+          <t>Jehangir Chowk to Budgam</t>
         </is>
       </c>
       <c r="D32" s="70" t="n">
@@ -42614,7 +42614,7 @@
       </c>
       <c r="C33" s="18" t="inlineStr">
         <is>
-          <t>QAMARWARI ↔ JEHANGIR CHOWK</t>
+          <t>Qamarwari to Jehangir Chowk</t>
         </is>
       </c>
       <c r="D33" s="67" t="n">
@@ -42637,7 +42637,7 @@
       </c>
       <c r="C34" s="20" t="inlineStr">
         <is>
-          <t>NARBAL ↔ JEHANGIR CHOWK</t>
+          <t>Narbal to Jehangir Chowk</t>
         </is>
       </c>
       <c r="D34" s="70" t="n">
@@ -42660,7 +42660,7 @@
       </c>
       <c r="C35" s="18" t="inlineStr">
         <is>
-          <t>QAMARWARI ↔ DALGATE</t>
+          <t>Qamarwari to Dalgate</t>
         </is>
       </c>
       <c r="D35" s="67" t="n">
@@ -42683,7 +42683,7 @@
       </c>
       <c r="C36" s="20" t="inlineStr">
         <is>
-          <t>PARIMPORA ↔ JEHANGIR CHOWK</t>
+          <t>Parimpora to Jehangir Chowk</t>
         </is>
       </c>
       <c r="D36" s="70" t="n">
@@ -42706,7 +42706,7 @@
       </c>
       <c r="C37" s="18" t="inlineStr">
         <is>
-          <t>QAMARWARI ↔ DALGATE</t>
+          <t>Qamarwari to Dalgate</t>
         </is>
       </c>
       <c r="D37" s="67" t="n">
@@ -42729,7 +42729,7 @@
       </c>
       <c r="C38" s="20" t="inlineStr">
         <is>
-          <t>JVC ↔ BATWARA</t>
+          <t>JVC to Batwara</t>
         </is>
       </c>
       <c r="D38" s="70" t="n">
@@ -42752,7 +42752,7 @@
       </c>
       <c r="C39" s="18" t="inlineStr">
         <is>
-          <t>NARBAL ↔ JEHANGIR CHOWK</t>
+          <t>Narbal to Jehangir Chowk</t>
         </is>
       </c>
       <c r="D39" s="67" t="n">
@@ -42775,7 +42775,7 @@
       </c>
       <c r="C40" s="20" t="inlineStr">
         <is>
-          <t>QAMARWARI ↔ DALGATE</t>
+          <t>Qamarwari to Dalgate</t>
         </is>
       </c>
       <c r="D40" s="70" t="n">
@@ -42798,7 +42798,7 @@
       </c>
       <c r="C41" s="18" t="inlineStr">
         <is>
-          <t>SAFAKADAL ↔ JEHANGIR CHOWK</t>
+          <t>Safakadal to Jehangir Chowk</t>
         </is>
       </c>
       <c r="D41" s="67" t="n">
@@ -42821,7 +42821,7 @@
       </c>
       <c r="C42" s="20" t="inlineStr">
         <is>
-          <t>GBS ↔ LAL CHOWK</t>
+          <t>GBS to LAL Chowk</t>
         </is>
       </c>
       <c r="D42" s="70" t="n">
@@ -42844,7 +42844,7 @@
       </c>
       <c r="C43" s="18" t="inlineStr">
         <is>
-          <t>PARIMPORA ↔ JAWAHAIRNAGAR</t>
+          <t>Parimpora to Jawahairnagar</t>
         </is>
       </c>
       <c r="D43" s="67" t="n">
@@ -42867,7 +42867,7 @@
       </c>
       <c r="C44" s="20" t="inlineStr">
         <is>
-          <t>QAMARWARI ↔ DALGATE</t>
+          <t>Qamarwari to Dalgate</t>
         </is>
       </c>
       <c r="D44" s="70" t="n">
@@ -42890,7 +42890,7 @@
       </c>
       <c r="C45" s="18" t="inlineStr">
         <is>
-          <t>PARIMPORA ↔ JAWAHAIRNAGAR</t>
+          <t>Parimpora to Jawahairnagar</t>
         </is>
       </c>
       <c r="D45" s="67" t="n">
@@ -42913,7 +42913,7 @@
       </c>
       <c r="C46" s="20" t="inlineStr">
         <is>
-          <t>QAMARWARI ↔ BAGHI MEHTAB</t>
+          <t>Qamarwari to Baghi Mehtab</t>
         </is>
       </c>
       <c r="D46" s="70" t="n">
@@ -42936,7 +42936,7 @@
       </c>
       <c r="C47" s="18" t="inlineStr">
         <is>
-          <t>PARIMPORA ↔ JAWAHIRNAGAR</t>
+          <t>Parimpora to Jawahirnagar</t>
         </is>
       </c>
       <c r="D47" s="67" t="n">
@@ -42959,7 +42959,7 @@
       </c>
       <c r="C48" s="20" t="inlineStr">
         <is>
-          <t>PARIMPORA ↔ JAWAHIRNAGAR</t>
+          <t>Parimpora to Jawahirnagar</t>
         </is>
       </c>
       <c r="D48" s="70" t="n">
@@ -42982,7 +42982,7 @@
       </c>
       <c r="C49" s="18" t="inlineStr">
         <is>
-          <t>SAFAKADAL ↔ JEHANGIR CHOWK</t>
+          <t>Safakadal to Jehangir Chowk</t>
         </is>
       </c>
       <c r="D49" s="67" t="n">
@@ -43005,7 +43005,7 @@
       </c>
       <c r="C50" s="20" t="inlineStr">
         <is>
-          <t>PARIMPORA ↔ JAWAHIRNAGAR</t>
+          <t>Parimpora to Jawahirnagar</t>
         </is>
       </c>
       <c r="D50" s="70" t="n">
@@ -43028,7 +43028,7 @@
       </c>
       <c r="C51" s="18" t="inlineStr">
         <is>
-          <t>QAMARWARI ↔ DALGATE</t>
+          <t>Qamarwari to Dalgate</t>
         </is>
       </c>
       <c r="D51" s="67" t="n">
@@ -43051,7 +43051,7 @@
       </c>
       <c r="C52" s="20" t="inlineStr">
         <is>
-          <t>SAFAKADAL ↔ JEHANGIR CHOWK</t>
+          <t>Safakadal to Jehangir Chowk</t>
         </is>
       </c>
       <c r="D52" s="70" t="n">
@@ -43074,7 +43074,7 @@
       </c>
       <c r="C53" s="18" t="inlineStr">
         <is>
-          <t>JEHANGIR CHOWK ↔ BUDGAM</t>
+          <t>Jehangir Chowk to Budgam</t>
         </is>
       </c>
       <c r="D53" s="67" t="n">
@@ -43097,7 +43097,7 @@
       </c>
       <c r="C54" s="20" t="inlineStr">
         <is>
-          <t>JEHANGIR CHOWK ↔ BUDGAM</t>
+          <t>Jehangir Chowk to Budgam</t>
         </is>
       </c>
       <c r="D54" s="70" t="n">
@@ -43120,7 +43120,7 @@
       </c>
       <c r="C55" s="18" t="inlineStr">
         <is>
-          <t>SAFAKADAL ↔ JEHANGIR CHOWK</t>
+          <t>Safakadal to Jehangir Chowk</t>
         </is>
       </c>
       <c r="D55" s="67" t="n">
@@ -43143,7 +43143,7 @@
       </c>
       <c r="C56" s="20" t="inlineStr">
         <is>
-          <t>JEHANGIR CHOWK ↔ BUDGAM</t>
+          <t>Jehangir Chowk to Budgam</t>
         </is>
       </c>
       <c r="D56" s="70" t="n">
@@ -43166,7 +43166,7 @@
       </c>
       <c r="C57" s="18" t="inlineStr">
         <is>
-          <t>SAFAKADAL ↔ JEHANGIR CHOWK</t>
+          <t>Safakadal to Jehangir Chowk</t>
         </is>
       </c>
       <c r="D57" s="67" t="n">
@@ -43189,7 +43189,7 @@
       </c>
       <c r="C58" s="20" t="inlineStr">
         <is>
-          <t>NARBAL ↔ JEHANGIR CHOWK</t>
+          <t>Narbal to Jehangir Chowk</t>
         </is>
       </c>
       <c r="D58" s="70" t="n">
@@ -43212,7 +43212,7 @@
       </c>
       <c r="C59" s="18" t="inlineStr">
         <is>
-          <t>JEHANGIR CHOWK ↔ JVC</t>
+          <t>Jehangir Chowk to JVC</t>
         </is>
       </c>
       <c r="D59" s="67" t="n">
@@ -43235,7 +43235,7 @@
       </c>
       <c r="C60" s="20" t="inlineStr">
         <is>
-          <t>PARIMPORA ↔ JAWAHIRNAGAR</t>
+          <t>Parimpora to Jawahirnagar</t>
         </is>
       </c>
       <c r="D60" s="70" t="n">
@@ -43258,7 +43258,7 @@
       </c>
       <c r="C61" s="18" t="inlineStr">
         <is>
-          <t>JEHANGIR CHOWK ↔ JVC</t>
+          <t>Jehangir Chowk to JVC</t>
         </is>
       </c>
       <c r="D61" s="67" t="n">
@@ -43281,7 +43281,7 @@
       </c>
       <c r="C62" s="20" t="inlineStr">
         <is>
-          <t>JEHANGIR CHOWK ↔ BUDGAM</t>
+          <t>Jehangir Chowk to Budgam</t>
         </is>
       </c>
       <c r="D62" s="70" t="n">
@@ -43304,7 +43304,7 @@
       </c>
       <c r="C63" s="18" t="inlineStr">
         <is>
-          <t>NARBAL ↔ JEHANGIR CHOWK</t>
+          <t>Narbal to Jehangir Chowk</t>
         </is>
       </c>
       <c r="D63" s="67" t="n">
@@ -43327,7 +43327,7 @@
       </c>
       <c r="C64" s="20" t="inlineStr">
         <is>
-          <t>JEHANGIR CHOWK ↔ BUDGAM</t>
+          <t>Jehangir Chowk to Budgam</t>
         </is>
       </c>
       <c r="D64" s="70" t="n">
@@ -43350,7 +43350,7 @@
       </c>
       <c r="C65" s="18" t="inlineStr">
         <is>
-          <t>RANGPORA ↔ DALGATE</t>
+          <t>Rangpora to Dalgate</t>
         </is>
       </c>
       <c r="D65" s="67" t="n">
@@ -43373,7 +43373,7 @@
       </c>
       <c r="C66" s="20" t="inlineStr">
         <is>
-          <t>NARBAL ↔ JEHANGIR CHOWK</t>
+          <t>Narbal to Jehangir Chowk</t>
         </is>
       </c>
       <c r="D66" s="70" t="n">
@@ -43396,7 +43396,7 @@
       </c>
       <c r="C67" s="18" t="inlineStr">
         <is>
-          <t>NARBAL ↔ JEHANGIR CHOWK</t>
+          <t>Narbal to Jehangir Chowk</t>
         </is>
       </c>
       <c r="D67" s="67" t="n">
@@ -43419,7 +43419,7 @@
       </c>
       <c r="C68" s="20" t="inlineStr">
         <is>
-          <t>JEHANGIR CHOWK ↔ BUDGAM</t>
+          <t>Jehangir Chowk to Budgam</t>
         </is>
       </c>
       <c r="D68" s="70" t="n">
@@ -43442,7 +43442,7 @@
       </c>
       <c r="C69" s="18" t="inlineStr">
         <is>
-          <t>NARBAL ↔ JEHANGIR CHOWK</t>
+          <t>Narbal to Jehangir Chowk</t>
         </is>
       </c>
       <c r="D69" s="67" t="n">
@@ -43465,7 +43465,7 @@
       </c>
       <c r="C70" s="20" t="inlineStr">
         <is>
-          <t>LAWAYPORA ↔ JEHANGIR CHOWK</t>
+          <t>Lawaypora to Jehangir Chowk</t>
         </is>
       </c>
       <c r="D70" s="70" t="n">
@@ -43488,7 +43488,7 @@
       </c>
       <c r="C71" s="18" t="inlineStr">
         <is>
-          <t>RANGPORA ↔ LALCHOWK</t>
+          <t>Rangpora to Lalchowk</t>
         </is>
       </c>
       <c r="D71" s="67" t="n">
@@ -43511,7 +43511,7 @@
       </c>
       <c r="C72" s="20" t="inlineStr">
         <is>
-          <t>RANGPORA ↔ LALCHOWK</t>
+          <t>Rangpora to Lalchowk</t>
         </is>
       </c>
       <c r="D72" s="70" t="n">
@@ -43534,7 +43534,7 @@
       </c>
       <c r="C73" s="18" t="inlineStr">
         <is>
-          <t>RANGPORA ↔ LALCHOWK</t>
+          <t>Rangpora to Lalchowk</t>
         </is>
       </c>
       <c r="D73" s="67" t="n">
@@ -43557,7 +43557,7 @@
       </c>
       <c r="C74" s="20" t="inlineStr">
         <is>
-          <t>JEHANGIR CHOWK ↔ BUDGAM</t>
+          <t>Jehangir Chowk to Budgam</t>
         </is>
       </c>
       <c r="D74" s="70" t="n">
@@ -43580,7 +43580,7 @@
       </c>
       <c r="C75" s="18" t="inlineStr">
         <is>
-          <t>RANGPORA ↔ LALCHOWK</t>
+          <t>Rangpora to Lalchowk</t>
         </is>
       </c>
       <c r="D75" s="67" t="n">
@@ -43603,7 +43603,7 @@
       </c>
       <c r="C76" s="20" t="inlineStr">
         <is>
-          <t>RANGPORA ↔ LALCHOWK</t>
+          <t>Rangpora to Lalchowk</t>
         </is>
       </c>
       <c r="D76" s="70" t="n">
@@ -43626,7 +43626,7 @@
       </c>
       <c r="C77" s="18" t="inlineStr">
         <is>
-          <t>NARBAL ↔ JEHANGIR CHOWK</t>
+          <t>Narbal to Jehangir Chowk</t>
         </is>
       </c>
       <c r="D77" s="67" t="n">
@@ -43649,7 +43649,7 @@
       </c>
       <c r="C78" s="20" t="inlineStr">
         <is>
-          <t>LAWAYPORA ↔ JEHANGIR CHOWK</t>
+          <t>Lawaypora to Jehangir Chowk</t>
         </is>
       </c>
       <c r="D78" s="70" t="n">
@@ -43672,7 +43672,7 @@
       </c>
       <c r="C79" s="18" t="inlineStr">
         <is>
-          <t>JEHANGIR CHOWK ↔ JVC</t>
+          <t>Jehangir Chowk to JVC</t>
         </is>
       </c>
       <c r="D79" s="67" t="n">
@@ -43695,7 +43695,7 @@
       </c>
       <c r="C80" s="20" t="inlineStr">
         <is>
-          <t>SAFAKADAL ↔ JEHANGIR CHOWK</t>
+          <t>Safakadal to Jehangir Chowk</t>
         </is>
       </c>
       <c r="D80" s="70" t="n">
@@ -43718,7 +43718,7 @@
       </c>
       <c r="C81" s="18" t="inlineStr">
         <is>
-          <t>JEHANGIR CHOWK ↔ JVC</t>
+          <t>Jehangir Chowk to JVC</t>
         </is>
       </c>
       <c r="D81" s="67" t="n">
@@ -43741,7 +43741,7 @@
       </c>
       <c r="C82" s="20" t="inlineStr">
         <is>
-          <t>PARIMPORA ↔ JAWAHIRNAGAR</t>
+          <t>Parimpora to Jawahirnagar</t>
         </is>
       </c>
       <c r="D82" s="70" t="n">
@@ -43764,7 +43764,7 @@
       </c>
       <c r="C83" s="18" t="inlineStr">
         <is>
-          <t>SAFAKADAL ↔ JEHANGIR CHOWK</t>
+          <t>Safakadal to Jehangir Chowk</t>
         </is>
       </c>
       <c r="D83" s="67" t="n">
@@ -43787,7 +43787,7 @@
       </c>
       <c r="C84" s="20" t="inlineStr">
         <is>
-          <t>SRINAGAR to CHOWKIBAL</t>
+          <t>Srinagar to Chowkibal</t>
         </is>
       </c>
       <c r="D84" s="70" t="n">
@@ -43810,7 +43810,7 @@
       </c>
       <c r="C85" s="18" t="inlineStr">
         <is>
-          <t>SRINAGAR to SAFAPORA SUMBAL</t>
+          <t>Srinagar to Safapora Sumbal</t>
         </is>
       </c>
       <c r="D85" s="67" t="n">
@@ -43948,7 +43948,7 @@
       </c>
       <c r="C91" s="18" t="inlineStr">
         <is>
-          <t>Batamaloo to DC Office Budgam</t>
+          <t>Batamaloo to Dc Office Budgam</t>
         </is>
       </c>
       <c r="D91" s="67" t="n">
@@ -44020,7 +44020,7 @@
       </c>
       <c r="C5" s="18" t="inlineStr">
         <is>
-          <t>PARIMPORA ↔ HAZRATBAL</t>
+          <t>Parimpora to Hazratbal</t>
         </is>
       </c>
       <c r="D5" s="67" t="inlineStr">
@@ -44040,7 +44040,7 @@
       </c>
       <c r="C6" s="20" t="inlineStr">
         <is>
-          <t>SOURA ↔ HAZRATBAL</t>
+          <t>Soura to Hazratbal</t>
         </is>
       </c>
       <c r="D6" s="70" t="inlineStr">
@@ -44060,7 +44060,7 @@
       </c>
       <c r="C7" s="18" t="inlineStr">
         <is>
-          <t>TRC ↔ HAZRATBAL</t>
+          <t>TRC to Hazratbal</t>
         </is>
       </c>
       <c r="D7" s="67" t="inlineStr">
@@ -44080,7 +44080,7 @@
       </c>
       <c r="C8" s="20" t="inlineStr">
         <is>
-          <t>HAZRATBAL ↔ LD</t>
+          <t>Hazratbal to LD</t>
         </is>
       </c>
       <c r="D8" s="70" t="inlineStr">
@@ -44100,7 +44100,7 @@
       </c>
       <c r="C9" s="18" t="inlineStr">
         <is>
-          <t>SOURA ↔ HAZRATBAL</t>
+          <t>Soura to Hazratbal</t>
         </is>
       </c>
       <c r="D9" s="67" t="inlineStr">
@@ -44120,7 +44120,7 @@
       </c>
       <c r="C10" s="20" t="inlineStr">
         <is>
-          <t>SOURA ↔ HAZRATBAL</t>
+          <t>Soura to Hazratbal</t>
         </is>
       </c>
       <c r="D10" s="70" t="inlineStr">
@@ -44140,7 +44140,7 @@
       </c>
       <c r="C11" s="18" t="inlineStr">
         <is>
-          <t>HAZRATBAL ↔ LD</t>
+          <t>Hazratbal to LD</t>
         </is>
       </c>
       <c r="D11" s="67" t="inlineStr">
@@ -44160,7 +44160,7 @@
       </c>
       <c r="C12" s="20" t="inlineStr">
         <is>
-          <t>HAZRATBAL ↔ LD</t>
+          <t>Hazratbal to LD</t>
         </is>
       </c>
       <c r="D12" s="70" t="inlineStr">
@@ -44180,7 +44180,7 @@
       </c>
       <c r="C13" s="18" t="inlineStr">
         <is>
-          <t>PARIMPORA ↔ HAZRATBAL</t>
+          <t>Parimpora to Hazratbal</t>
         </is>
       </c>
       <c r="D13" s="67" t="inlineStr">
@@ -44200,7 +44200,7 @@
       </c>
       <c r="C14" s="20" t="inlineStr">
         <is>
-          <t>QAMARWARI ↔ HAZRATBAL</t>
+          <t>Qamarwari to Hazratbal</t>
         </is>
       </c>
       <c r="D14" s="70" t="inlineStr">
@@ -44220,7 +44220,7 @@
       </c>
       <c r="C15" s="18" t="inlineStr">
         <is>
-          <t>HAZRATBAL ↔ BONE JOINT HOSPITAL BARZALLA</t>
+          <t>Hazratbal to Bone Joint Hospital Barzalla</t>
         </is>
       </c>
       <c r="D15" s="67" t="inlineStr">
@@ -44240,7 +44240,7 @@
       </c>
       <c r="C16" s="20" t="inlineStr">
         <is>
-          <t>HAZRATBAL ↔ LD</t>
+          <t>Hazratbal to LD</t>
         </is>
       </c>
       <c r="D16" s="70" t="inlineStr">
@@ -44260,7 +44260,7 @@
       </c>
       <c r="C17" s="18" t="inlineStr">
         <is>
-          <t>HAZRATBAL ↔ LD</t>
+          <t>Hazratbal to LD</t>
         </is>
       </c>
       <c r="D17" s="67" t="inlineStr">
@@ -44280,7 +44280,7 @@
       </c>
       <c r="C18" s="20" t="inlineStr">
         <is>
-          <t>HAZRATBAL ↔ LD</t>
+          <t>Hazratbal to LD</t>
         </is>
       </c>
       <c r="D18" s="70" t="inlineStr">
@@ -44300,7 +44300,7 @@
       </c>
       <c r="C19" s="18" t="inlineStr">
         <is>
-          <t>HAZRATBAL ↔ LD</t>
+          <t>Hazratbal to LD</t>
         </is>
       </c>
       <c r="D19" s="67" t="inlineStr">
@@ -44320,7 +44320,7 @@
       </c>
       <c r="C20" s="20" t="inlineStr">
         <is>
-          <t>HAZRATBAL ↔ LD</t>
+          <t>Hazratbal to LD</t>
         </is>
       </c>
       <c r="D20" s="70" t="inlineStr">
@@ -44340,7 +44340,7 @@
       </c>
       <c r="C21" s="18" t="inlineStr">
         <is>
-          <t>HAZRATBAL ↔ LD</t>
+          <t>Hazratbal to LD</t>
         </is>
       </c>
       <c r="D21" s="67" t="inlineStr">
@@ -44360,7 +44360,7 @@
       </c>
       <c r="C22" s="20" t="inlineStr">
         <is>
-          <t>HAZRATBAL ↔ LD</t>
+          <t>Hazratbal to LD</t>
         </is>
       </c>
       <c r="D22" s="70" t="inlineStr">
@@ -44380,7 +44380,7 @@
       </c>
       <c r="C23" s="18" t="inlineStr">
         <is>
-          <t>HAZRATBAL ↔ LD</t>
+          <t>Hazratbal to LD</t>
         </is>
       </c>
       <c r="D23" s="67" t="inlineStr">
@@ -44400,7 +44400,7 @@
       </c>
       <c r="C24" s="20" t="inlineStr">
         <is>
-          <t>HAZRATBAL ↔ LD</t>
+          <t>Hazratbal to LD</t>
         </is>
       </c>
       <c r="D24" s="70" t="inlineStr">
@@ -44420,7 +44420,7 @@
       </c>
       <c r="C25" s="18" t="inlineStr">
         <is>
-          <t>HAZRATBAL ↔ LD</t>
+          <t>Hazratbal to LD</t>
         </is>
       </c>
       <c r="D25" s="67" t="inlineStr">
@@ -44440,7 +44440,7 @@
       </c>
       <c r="C26" s="20" t="inlineStr">
         <is>
-          <t>HAZRATBAL ↔ LD</t>
+          <t>Hazratbal to LD</t>
         </is>
       </c>
       <c r="D26" s="70" t="inlineStr">
@@ -44460,7 +44460,7 @@
       </c>
       <c r="C27" s="18" t="inlineStr">
         <is>
-          <t>CHANAPORA ↔ SOURA</t>
+          <t>Chanapora to Soura</t>
         </is>
       </c>
       <c r="D27" s="67" t="inlineStr">
@@ -44480,7 +44480,7 @@
       </c>
       <c r="C28" s="20" t="inlineStr">
         <is>
-          <t>HAZRATBAL ↔ LD</t>
+          <t>Hazratbal to LD</t>
         </is>
       </c>
       <c r="D28" s="70" t="inlineStr">
@@ -44500,7 +44500,7 @@
       </c>
       <c r="C29" s="18" t="inlineStr">
         <is>
-          <t>HAZRATBAL ↔ LD</t>
+          <t>Hazratbal to LD</t>
         </is>
       </c>
       <c r="D29" s="67" t="inlineStr">
@@ -44520,7 +44520,7 @@
       </c>
       <c r="C30" s="20" t="inlineStr">
         <is>
-          <t>HAZRATBAL ↔ LD</t>
+          <t>Hazratbal to LD</t>
         </is>
       </c>
       <c r="D30" s="70" t="inlineStr">
@@ -44540,7 +44540,7 @@
       </c>
       <c r="C31" s="18" t="inlineStr">
         <is>
-          <t>HAZRATBAL ↔ LD</t>
+          <t>Hazratbal to LD</t>
         </is>
       </c>
       <c r="D31" s="67" t="inlineStr">
@@ -44560,7 +44560,7 @@
       </c>
       <c r="C32" s="20" t="inlineStr">
         <is>
-          <t>HAZRATBAL ↔ LD</t>
+          <t>Hazratbal to LD</t>
         </is>
       </c>
       <c r="D32" s="70" t="inlineStr">
@@ -44580,7 +44580,7 @@
       </c>
       <c r="C33" s="18" t="inlineStr">
         <is>
-          <t>HAZRATBAL ↔ LD</t>
+          <t>Hazratbal to LD</t>
         </is>
       </c>
       <c r="D33" s="67" t="inlineStr">
@@ -44600,7 +44600,7 @@
       </c>
       <c r="C34" s="20" t="inlineStr">
         <is>
-          <t>HAZRATBAL ↔ LD</t>
+          <t>Hazratbal to LD</t>
         </is>
       </c>
       <c r="D34" s="70" t="inlineStr">
@@ -44620,7 +44620,7 @@
       </c>
       <c r="C35" s="18" t="inlineStr">
         <is>
-          <t>HAZRATBAL ↔ LD</t>
+          <t>Hazratbal to LD</t>
         </is>
       </c>
       <c r="D35" s="67" t="inlineStr">
@@ -44640,7 +44640,7 @@
       </c>
       <c r="C36" s="20" t="inlineStr">
         <is>
-          <t>HAZRATBAL ↔ LD</t>
+          <t>Hazratbal to LD</t>
         </is>
       </c>
       <c r="D36" s="70" t="inlineStr">
@@ -44660,7 +44660,7 @@
       </c>
       <c r="C37" s="18" t="inlineStr">
         <is>
-          <t>SOURA ↔ HAZRATBAL</t>
+          <t>Soura to Hazratbal</t>
         </is>
       </c>
       <c r="D37" s="67" t="inlineStr">
@@ -44680,7 +44680,7 @@
       </c>
       <c r="C38" s="20" t="inlineStr">
         <is>
-          <t>PARIMPORA ↔ HAZRATBAL</t>
+          <t>Parimpora to Hazratbal</t>
         </is>
       </c>
       <c r="D38" s="70" t="inlineStr">
@@ -44700,7 +44700,7 @@
       </c>
       <c r="C39" s="18" t="inlineStr">
         <is>
-          <t>PARIMPORA ↔ HAZRATBAL</t>
+          <t>Parimpora to Hazratbal</t>
         </is>
       </c>
       <c r="D39" s="67" t="inlineStr">
@@ -44720,7 +44720,7 @@
       </c>
       <c r="C40" s="20" t="inlineStr">
         <is>
-          <t>HAZRATBAL ↔ LD</t>
+          <t>Hazratbal to LD</t>
         </is>
       </c>
       <c r="D40" s="70" t="inlineStr">
@@ -44740,7 +44740,7 @@
       </c>
       <c r="C41" s="18" t="inlineStr">
         <is>
-          <t>HAZRATBAL ↔ LD</t>
+          <t>Hazratbal to LD</t>
         </is>
       </c>
       <c r="D41" s="67" t="inlineStr">
@@ -44760,7 +44760,7 @@
       </c>
       <c r="C42" s="20" t="inlineStr">
         <is>
-          <t>HAZRATBAL ↔ LD</t>
+          <t>Hazratbal to LD</t>
         </is>
       </c>
       <c r="D42" s="70" t="inlineStr">
@@ -44780,7 +44780,7 @@
       </c>
       <c r="C43" s="18" t="inlineStr">
         <is>
-          <t>HAZRATBAL ↔ LD</t>
+          <t>Hazratbal to LD</t>
         </is>
       </c>
       <c r="D43" s="67" t="inlineStr">
@@ -44800,7 +44800,7 @@
       </c>
       <c r="C44" s="20" t="inlineStr">
         <is>
-          <t>HAZRATBAL ↔ LD</t>
+          <t>Hazratbal to LD</t>
         </is>
       </c>
       <c r="D44" s="70" t="inlineStr">
@@ -44820,7 +44820,7 @@
       </c>
       <c r="C45" s="18" t="inlineStr">
         <is>
-          <t>HAZRATBAL ↔ LD</t>
+          <t>Hazratbal to LD</t>
         </is>
       </c>
       <c r="D45" s="67" t="inlineStr">
@@ -44840,7 +44840,7 @@
       </c>
       <c r="C46" s="20" t="inlineStr">
         <is>
-          <t>HAZRATBAL ↔ LD</t>
+          <t>Hazratbal to LD</t>
         </is>
       </c>
       <c r="D46" s="70" t="inlineStr">
@@ -44860,7 +44860,7 @@
       </c>
       <c r="C47" s="18" t="inlineStr">
         <is>
-          <t>HAZRATBAL ↔ LD</t>
+          <t>Hazratbal to LD</t>
         </is>
       </c>
       <c r="D47" s="67" t="inlineStr">
@@ -44880,7 +44880,7 @@
       </c>
       <c r="C48" s="20" t="inlineStr">
         <is>
-          <t>HAZRATBAL ↔ LD</t>
+          <t>Hazratbal to LD</t>
         </is>
       </c>
       <c r="D48" s="70" t="inlineStr">
@@ -44900,7 +44900,7 @@
       </c>
       <c r="C49" s="18" t="inlineStr">
         <is>
-          <t>HAZRATBAL ↔ LD</t>
+          <t>Hazratbal to LD</t>
         </is>
       </c>
       <c r="D49" s="67" t="inlineStr">
@@ -44920,7 +44920,7 @@
       </c>
       <c r="C50" s="20" t="inlineStr">
         <is>
-          <t>HAZRATBAL ↔ LD</t>
+          <t>Hazratbal to LD</t>
         </is>
       </c>
       <c r="D50" s="70" t="inlineStr">
@@ -44940,7 +44940,7 @@
       </c>
       <c r="C51" s="18" t="inlineStr">
         <is>
-          <t>HAZRATBAL ↔ LD</t>
+          <t>Hazratbal to LD</t>
         </is>
       </c>
       <c r="D51" s="67" t="inlineStr">
@@ -44960,7 +44960,7 @@
       </c>
       <c r="C52" s="20" t="inlineStr">
         <is>
-          <t>HAZRATBAL ↔ LD</t>
+          <t>Hazratbal to LD</t>
         </is>
       </c>
       <c r="D52" s="70" t="inlineStr">
@@ -44980,7 +44980,7 @@
       </c>
       <c r="C53" s="18" t="inlineStr">
         <is>
-          <t>HAZRATBAL ↔ LD</t>
+          <t>Hazratbal to LD</t>
         </is>
       </c>
       <c r="D53" s="67" t="inlineStr">
@@ -45000,7 +45000,7 @@
       </c>
       <c r="C54" s="20" t="inlineStr">
         <is>
-          <t>HAZRATBAL ↔ LD</t>
+          <t>Hazratbal to LD</t>
         </is>
       </c>
       <c r="D54" s="70" t="inlineStr">
@@ -45020,7 +45020,7 @@
       </c>
       <c r="C55" s="18" t="inlineStr">
         <is>
-          <t>HAZRATBAL ↔ LD</t>
+          <t>Hazratbal to LD</t>
         </is>
       </c>
       <c r="D55" s="67" t="inlineStr">
@@ -45040,7 +45040,7 @@
       </c>
       <c r="C56" s="20" t="inlineStr">
         <is>
-          <t>HAZRATBAL ↔ LD</t>
+          <t>Hazratbal to LD</t>
         </is>
       </c>
       <c r="D56" s="70" t="inlineStr">
@@ -45060,7 +45060,7 @@
       </c>
       <c r="C57" s="18" t="inlineStr">
         <is>
-          <t>SOURA ↔ HAZRATBAL</t>
+          <t>Soura to Hazratbal</t>
         </is>
       </c>
       <c r="D57" s="67" t="inlineStr">
@@ -45080,7 +45080,7 @@
       </c>
       <c r="C58" s="20" t="inlineStr">
         <is>
-          <t>SOURA ↔ HAZRATBAL</t>
+          <t>Soura to Hazratbal</t>
         </is>
       </c>
       <c r="D58" s="70" t="inlineStr">
@@ -45100,7 +45100,7 @@
       </c>
       <c r="C59" s="18" t="inlineStr">
         <is>
-          <t>HAZRATBAL ↔ LD</t>
+          <t>Hazratbal to LD</t>
         </is>
       </c>
       <c r="D59" s="67" t="inlineStr">
@@ -45120,7 +45120,7 @@
       </c>
       <c r="C60" s="20" t="inlineStr">
         <is>
-          <t>SOURA ↔ HAZRATBAL</t>
+          <t>Soura to Hazratbal</t>
         </is>
       </c>
       <c r="D60" s="70" t="inlineStr">
@@ -45140,7 +45140,7 @@
       </c>
       <c r="C61" s="18" t="inlineStr">
         <is>
-          <t>CHANAPORA ↔ SOURA</t>
+          <t>Chanapora to Soura</t>
         </is>
       </c>
       <c r="D61" s="67" t="inlineStr">
@@ -45160,7 +45160,7 @@
       </c>
       <c r="C62" s="20" t="inlineStr">
         <is>
-          <t>HAZRATBAL ↔ LD</t>
+          <t>Hazratbal to LD</t>
         </is>
       </c>
       <c r="D62" s="70" t="inlineStr">
@@ -45180,7 +45180,7 @@
       </c>
       <c r="C63" s="18" t="inlineStr">
         <is>
-          <t>SOURA ↔ HAZRATBAL</t>
+          <t>Soura to Hazratbal</t>
         </is>
       </c>
       <c r="D63" s="67" t="inlineStr">
@@ -45200,7 +45200,7 @@
       </c>
       <c r="C64" s="20" t="inlineStr">
         <is>
-          <t>TRC ↔ HAZRATBAL</t>
+          <t>TRC to Hazratbal</t>
         </is>
       </c>
       <c r="D64" s="70" t="inlineStr">
@@ -45220,7 +45220,7 @@
       </c>
       <c r="C65" s="18" t="inlineStr">
         <is>
-          <t>TRC ↔ HAZRATBAL</t>
+          <t>TRC to Hazratbal</t>
         </is>
       </c>
       <c r="D65" s="67" t="inlineStr">
@@ -45240,7 +45240,7 @@
       </c>
       <c r="C66" s="20" t="inlineStr">
         <is>
-          <t>SOURA ↔ HAZRATBAL</t>
+          <t>Soura to Hazratbal</t>
         </is>
       </c>
       <c r="D66" s="70" t="inlineStr">
@@ -45260,7 +45260,7 @@
       </c>
       <c r="C67" s="18" t="inlineStr">
         <is>
-          <t>SOURA ↔ HAZRATBAL</t>
+          <t>Soura to Hazratbal</t>
         </is>
       </c>
       <c r="D67" s="67" t="inlineStr">
@@ -45280,7 +45280,7 @@
       </c>
       <c r="C68" s="20" t="inlineStr">
         <is>
-          <t>SOURA ↔ HAZRATBAL</t>
+          <t>Soura to Hazratbal</t>
         </is>
       </c>
       <c r="D68" s="70" t="inlineStr">
@@ -45300,7 +45300,7 @@
       </c>
       <c r="C69" s="18" t="inlineStr">
         <is>
-          <t>SRINAGAR to CHEWDARA</t>
+          <t>Srinagar to Chewdara</t>
         </is>
       </c>
       <c r="D69" s="67" t="inlineStr">
@@ -45320,7 +45320,7 @@
       </c>
       <c r="C70" s="20" t="inlineStr">
         <is>
-          <t>SRINAGAR to HARWAN</t>
+          <t>Srinagar to Harwan</t>
         </is>
       </c>
       <c r="D70" s="70" t="inlineStr">
@@ -45340,7 +45340,7 @@
       </c>
       <c r="C71" s="18" t="inlineStr">
         <is>
-          <t>SRINAGAR to HARWAN</t>
+          <t>Srinagar to Harwan</t>
         </is>
       </c>
       <c r="D71" s="67" t="inlineStr">
@@ -45360,7 +45360,7 @@
       </c>
       <c r="C72" s="20" t="inlineStr">
         <is>
-          <t>SRINAGAR to HARWAN</t>
+          <t>Srinagar to Harwan</t>
         </is>
       </c>
       <c r="D72" s="70" t="inlineStr">

--- a/public/route-rationalization-kashmir/Kashmir_Route_Frequency_Plan_v3.3.7_RTO.xlsx
+++ b/public/route-rationalization-kashmir/Kashmir_Route_Frequency_Plan_v3.3.7_RTO.xlsx
@@ -883,7 +883,7 @@
     <row r="9">
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>Version: v3.3.7  |  Generated: 30 May 2026</t>
+          <t>Version: v3.3.7  |  Generated: 03 Jun 2026</t>
         </is>
       </c>
     </row>
@@ -1529,7 +1529,7 @@
     <row r="2">
       <c r="A2" s="29" t="inlineStr">
         <is>
-          <t>PWSP08091215</t>
+          <t>SRSR10105860</t>
         </is>
       </c>
       <c r="B2" s="29" t="inlineStr">
@@ -1855,7 +1855,7 @@
     <row r="5">
       <c r="A5" s="36" t="inlineStr">
         <is>
-          <t>SRSP10093415</t>
+          <t>SRSR10103460</t>
         </is>
       </c>
       <c r="B5" s="36" t="inlineStr">
@@ -1961,7 +1961,7 @@
     <row r="6">
       <c r="A6" s="46" t="inlineStr">
         <is>
-          <t>PWGB08051203</t>
+          <t>SRGB10055803</t>
         </is>
       </c>
       <c r="B6" s="46" t="inlineStr">
@@ -2067,7 +2067,7 @@
     <row r="7">
       <c r="A7" s="36" t="inlineStr">
         <is>
-          <t>PWGB08051204</t>
+          <t>SRGB10055804</t>
         </is>
       </c>
       <c r="B7" s="36" t="inlineStr">
@@ -2173,7 +2173,7 @@
     <row r="8">
       <c r="A8" s="46" t="inlineStr">
         <is>
-          <t>PWGB08051204</t>
+          <t>SRGB10055804</t>
         </is>
       </c>
       <c r="B8" s="46" t="inlineStr">
@@ -2279,7 +2279,7 @@
     <row r="9">
       <c r="A9" s="36" t="inlineStr">
         <is>
-          <t>SRAN10013409</t>
+          <t>SRSR10103462</t>
         </is>
       </c>
       <c r="B9" s="36" t="inlineStr">
@@ -2385,7 +2385,7 @@
     <row r="10">
       <c r="A10" s="46" t="inlineStr">
         <is>
-          <t>SRPW10082512</t>
+          <t>SRSR10102558</t>
         </is>
       </c>
       <c r="B10" s="46" t="inlineStr">
@@ -2491,7 +2491,7 @@
     <row r="11">
       <c r="A11" s="29" t="inlineStr">
         <is>
-          <t>PWSP08091215</t>
+          <t>SRSR10105860</t>
         </is>
       </c>
       <c r="B11" s="29" t="inlineStr">
@@ -2601,7 +2601,7 @@
     <row r="12">
       <c r="A12" s="29" t="inlineStr">
         <is>
-          <t>PWSP08091215</t>
+          <t>SRSR10105860</t>
         </is>
       </c>
       <c r="B12" s="29" t="inlineStr">
@@ -2711,7 +2711,7 @@
     <row r="13">
       <c r="A13" s="36" t="inlineStr">
         <is>
-          <t>PWSR08101218</t>
+          <t>SRSR10105818</t>
         </is>
       </c>
       <c r="B13" s="36" t="inlineStr">
@@ -2923,7 +2923,7 @@
     <row r="15">
       <c r="A15" s="29" t="inlineStr">
         <is>
-          <t>SRSP10091815</t>
+          <t>SRSR10101860</t>
         </is>
       </c>
       <c r="B15" s="29" t="inlineStr">
@@ -3033,7 +3033,7 @@
     <row r="16">
       <c r="A16" s="46" t="inlineStr">
         <is>
-          <t>PWAN08011213</t>
+          <t>SRAN10015813</t>
         </is>
       </c>
       <c r="B16" s="46" t="inlineStr">
@@ -3139,7 +3139,7 @@
     <row r="17">
       <c r="A17" s="29" t="inlineStr">
         <is>
-          <t>PWSP08091215</t>
+          <t>SRSR10105860</t>
         </is>
       </c>
       <c r="B17" s="29" t="inlineStr">
@@ -3249,7 +3249,7 @@
     <row r="18">
       <c r="A18" s="46" t="inlineStr">
         <is>
-          <t>KWSP07090815</t>
+          <t>SRSR10106360</t>
         </is>
       </c>
       <c r="B18" s="46" t="inlineStr">
@@ -3355,7 +3355,7 @@
     <row r="19">
       <c r="A19" s="51" t="inlineStr">
         <is>
-          <t>SRSP10092512</t>
+          <t>SRSR10102559</t>
         </is>
       </c>
       <c r="B19" s="51" t="inlineStr">
@@ -3461,7 +3461,7 @@
     <row r="20">
       <c r="A20" s="55" t="inlineStr">
         <is>
-          <t>SRSP10092512</t>
+          <t>SRSR10102559</t>
         </is>
       </c>
       <c r="B20" s="55" t="inlineStr">
@@ -3567,7 +3567,7 @@
     <row r="21">
       <c r="A21" s="29" t="inlineStr">
         <is>
-          <t>PWBG08021221</t>
+          <t>SRBG10025821</t>
         </is>
       </c>
       <c r="B21" s="29" t="inlineStr">
@@ -3677,7 +3677,7 @@
     <row r="22">
       <c r="A22" s="29" t="inlineStr">
         <is>
-          <t>PWSR08101218</t>
+          <t>SRSR10105818</t>
         </is>
       </c>
       <c r="B22" s="29" t="inlineStr">
@@ -3787,7 +3787,7 @@
     <row r="23">
       <c r="A23" s="29" t="inlineStr">
         <is>
-          <t>PWSP08091215</t>
+          <t>SRSR10105860</t>
         </is>
       </c>
       <c r="B23" s="29" t="inlineStr">
@@ -3897,7 +3897,7 @@
     <row r="24">
       <c r="A24" s="55" t="inlineStr">
         <is>
-          <t>SRSP10092512</t>
+          <t>SRSR10102559</t>
         </is>
       </c>
       <c r="B24" s="55" t="inlineStr">
@@ -4003,7 +4003,7 @@
     <row r="25">
       <c r="A25" s="51" t="inlineStr">
         <is>
-          <t>SRSP10092512</t>
+          <t>SRSR10102559</t>
         </is>
       </c>
       <c r="B25" s="51" t="inlineStr">
@@ -4215,7 +4215,7 @@
     <row r="27">
       <c r="A27" s="51" t="inlineStr">
         <is>
-          <t>SRSP10092512</t>
+          <t>SRSR10102559</t>
         </is>
       </c>
       <c r="B27" s="51" t="inlineStr">
@@ -4537,7 +4537,7 @@
     <row r="30">
       <c r="A30" s="29" t="inlineStr">
         <is>
-          <t>PWSP08091215</t>
+          <t>SRSR10105860</t>
         </is>
       </c>
       <c r="B30" s="29" t="inlineStr">
@@ -4647,7 +4647,7 @@
     <row r="31">
       <c r="A31" s="29" t="inlineStr">
         <is>
-          <t>PWSP08091215</t>
+          <t>SRSR10105860</t>
         </is>
       </c>
       <c r="B31" s="29" t="inlineStr">
@@ -4757,7 +4757,7 @@
     <row r="32">
       <c r="A32" s="46" t="inlineStr">
         <is>
-          <t>PWAN08011213</t>
+          <t>SRAN10015813</t>
         </is>
       </c>
       <c r="B32" s="46" t="inlineStr">
@@ -4863,7 +4863,7 @@
     <row r="33">
       <c r="A33" s="29" t="inlineStr">
         <is>
-          <t>PWSR08101218</t>
+          <t>SRSR10105818</t>
         </is>
       </c>
       <c r="B33" s="29" t="inlineStr">
@@ -4973,7 +4973,7 @@
     <row r="34">
       <c r="A34" s="29" t="inlineStr">
         <is>
-          <t>SRSP10095015</t>
+          <t>SRSR10105060</t>
         </is>
       </c>
       <c r="B34" s="29" t="inlineStr">
@@ -5083,7 +5083,7 @@
     <row r="35">
       <c r="A35" s="29" t="inlineStr">
         <is>
-          <t>BRAN04010109</t>
+          <t>BRSR04100162</t>
         </is>
       </c>
       <c r="B35" s="29" t="inlineStr">
@@ -5193,7 +5193,7 @@
     <row r="36">
       <c r="A36" s="55" t="inlineStr">
         <is>
-          <t>SRSP10092512</t>
+          <t>SRSR10102559</t>
         </is>
       </c>
       <c r="B36" s="55" t="inlineStr">
@@ -5617,7 +5617,7 @@
     <row r="40">
       <c r="A40" s="29" t="inlineStr">
         <is>
-          <t>PWSP08091215</t>
+          <t>SRSR10105860</t>
         </is>
       </c>
       <c r="B40" s="29" t="inlineStr">
@@ -5939,7 +5939,7 @@
     <row r="43">
       <c r="A43" s="29" t="inlineStr">
         <is>
-          <t>PWBG08021221</t>
+          <t>SRBG10025821</t>
         </is>
       </c>
       <c r="B43" s="29" t="inlineStr">
@@ -6049,7 +6049,7 @@
     <row r="44">
       <c r="A44" s="29" t="inlineStr">
         <is>
-          <t>PWSR08101206</t>
+          <t>SRSR10105806</t>
         </is>
       </c>
       <c r="B44" s="29" t="inlineStr">
@@ -6489,7 +6489,7 @@
     <row r="48">
       <c r="A48" s="29" t="inlineStr">
         <is>
-          <t>PWSP08091215</t>
+          <t>SRSR10105860</t>
         </is>
       </c>
       <c r="B48" s="29" t="inlineStr">
@@ -6709,7 +6709,7 @@
     <row r="50">
       <c r="A50" s="46" t="inlineStr">
         <is>
-          <t>SRSP10093415</t>
+          <t>SRSR10103460</t>
         </is>
       </c>
       <c r="B50" s="46" t="inlineStr">
@@ -6921,7 +6921,7 @@
     <row r="52">
       <c r="A52" s="29" t="inlineStr">
         <is>
-          <t>SRSP10091815</t>
+          <t>SRSR10101860</t>
         </is>
       </c>
       <c r="B52" s="29" t="inlineStr">
@@ -7031,7 +7031,7 @@
     <row r="53">
       <c r="A53" s="29" t="inlineStr">
         <is>
-          <t>SRSP10091815</t>
+          <t>SRSR10101860</t>
         </is>
       </c>
       <c r="B53" s="29" t="inlineStr">
@@ -8307,7 +8307,7 @@
     <row r="65">
       <c r="A65" s="36" t="inlineStr">
         <is>
-          <t>PWSR08101225</t>
+          <t>SRSR10105825</t>
         </is>
       </c>
       <c r="B65" s="36" t="inlineStr">
@@ -8731,7 +8731,7 @@
     <row r="69">
       <c r="A69" s="36" t="inlineStr">
         <is>
-          <t>SPGB09052002</t>
+          <t>SRGB10056102</t>
         </is>
       </c>
       <c r="B69" s="36" t="inlineStr">
@@ -8837,7 +8837,7 @@
     <row r="70">
       <c r="A70" s="46" t="inlineStr">
         <is>
-          <t>SPGB09052002</t>
+          <t>SRGB10056102</t>
         </is>
       </c>
       <c r="B70" s="46" t="inlineStr">
@@ -10239,7 +10239,7 @@
     <row r="83">
       <c r="A83" s="51" t="inlineStr">
         <is>
-          <t>SRSP10092512</t>
+          <t>SRSR10102559</t>
         </is>
       </c>
       <c r="B83" s="51" t="inlineStr">
@@ -10663,7 +10663,7 @@
     <row r="87">
       <c r="A87" s="36" t="inlineStr">
         <is>
-          <t>PWSR08101225</t>
+          <t>SRSR10105825</t>
         </is>
       </c>
       <c r="B87" s="36" t="inlineStr">
@@ -10769,7 +10769,7 @@
     <row r="88">
       <c r="A88" s="46" t="inlineStr">
         <is>
-          <t>PWSR08101225</t>
+          <t>SRSR10105825</t>
         </is>
       </c>
       <c r="B88" s="46" t="inlineStr">
@@ -11413,7 +11413,7 @@
     <row r="94">
       <c r="A94" s="46" t="inlineStr">
         <is>
-          <t>PWSR08101225</t>
+          <t>SRSR10105825</t>
         </is>
       </c>
       <c r="B94" s="46" t="inlineStr">
@@ -11519,7 +11519,7 @@
     <row r="95">
       <c r="A95" s="36" t="inlineStr">
         <is>
-          <t>SRSP10093415</t>
+          <t>SRSR10103460</t>
         </is>
       </c>
       <c r="B95" s="36" t="inlineStr">
@@ -11625,7 +11625,7 @@
     <row r="96">
       <c r="A96" s="46" t="inlineStr">
         <is>
-          <t>SRSP10093415</t>
+          <t>SRSR10103460</t>
         </is>
       </c>
       <c r="B96" s="46" t="inlineStr">
@@ -11731,7 +11731,7 @@
     <row r="97">
       <c r="A97" s="36" t="inlineStr">
         <is>
-          <t>SRSP10093415</t>
+          <t>SRSR10103460</t>
         </is>
       </c>
       <c r="B97" s="36" t="inlineStr">
@@ -11837,7 +11837,7 @@
     <row r="98">
       <c r="A98" s="55" t="inlineStr">
         <is>
-          <t>SPSR09101211</t>
+          <t>SRSR10105965</t>
         </is>
       </c>
       <c r="B98" s="55" t="inlineStr">
@@ -12371,7 +12371,7 @@
     <row r="103">
       <c r="A103" s="29" t="inlineStr">
         <is>
-          <t>SRSP10091815</t>
+          <t>SRSR10101860</t>
         </is>
       </c>
       <c r="B103" s="29" t="inlineStr">
@@ -12481,7 +12481,7 @@
     <row r="104">
       <c r="A104" s="29" t="inlineStr">
         <is>
-          <t>SRSP10091815</t>
+          <t>SRSR10101860</t>
         </is>
       </c>
       <c r="B104" s="29" t="inlineStr">
@@ -13129,7 +13129,7 @@
     <row r="110">
       <c r="A110" s="46" t="inlineStr">
         <is>
-          <t>SRSP10093415</t>
+          <t>SRSR10103460</t>
         </is>
       </c>
       <c r="B110" s="46" t="inlineStr">
@@ -13235,7 +13235,7 @@
     <row r="111">
       <c r="A111" s="36" t="inlineStr">
         <is>
-          <t>SRSP10093415</t>
+          <t>SRSR10103460</t>
         </is>
       </c>
       <c r="B111" s="36" t="inlineStr">
@@ -13341,7 +13341,7 @@
     <row r="112">
       <c r="A112" s="46" t="inlineStr">
         <is>
-          <t>SRSP10093415</t>
+          <t>SRSR10103460</t>
         </is>
       </c>
       <c r="B112" s="46" t="inlineStr">
@@ -13447,7 +13447,7 @@
     <row r="113">
       <c r="A113" s="29" t="inlineStr">
         <is>
-          <t>SRSP10091815</t>
+          <t>SRSR10101860</t>
         </is>
       </c>
       <c r="B113" s="29" t="inlineStr">
@@ -13663,7 +13663,7 @@
     <row r="115">
       <c r="A115" s="29" t="inlineStr">
         <is>
-          <t>SRSP10091815</t>
+          <t>SRSR10101860</t>
         </is>
       </c>
       <c r="B115" s="29" t="inlineStr">
@@ -13883,7 +13883,7 @@
     <row r="117">
       <c r="A117" s="29" t="inlineStr">
         <is>
-          <t>SRSP10091815</t>
+          <t>SRSR10101860</t>
         </is>
       </c>
       <c r="B117" s="29" t="inlineStr">
@@ -13993,7 +13993,7 @@
     <row r="118">
       <c r="A118" s="29" t="inlineStr">
         <is>
-          <t>SRSP10091815</t>
+          <t>SRSR10101860</t>
         </is>
       </c>
       <c r="B118" s="29" t="inlineStr">
@@ -14103,7 +14103,7 @@
     <row r="119">
       <c r="A119" s="29" t="inlineStr">
         <is>
-          <t>SRSP10091815</t>
+          <t>SRSR10101860</t>
         </is>
       </c>
       <c r="B119" s="29" t="inlineStr">
@@ -14653,7 +14653,7 @@
     <row r="124">
       <c r="A124" s="29" t="inlineStr">
         <is>
-          <t>SRSP10091815</t>
+          <t>SRSR10101860</t>
         </is>
       </c>
       <c r="B124" s="29" t="inlineStr">
@@ -14763,7 +14763,7 @@
     <row r="125">
       <c r="A125" s="29" t="inlineStr">
         <is>
-          <t>SRSP10091815</t>
+          <t>SRSR10101860</t>
         </is>
       </c>
       <c r="B125" s="29" t="inlineStr">
@@ -14873,7 +14873,7 @@
     <row r="126">
       <c r="A126" s="29" t="inlineStr">
         <is>
-          <t>SRSP10091815</t>
+          <t>SRSR10101860</t>
         </is>
       </c>
       <c r="B126" s="29" t="inlineStr">
@@ -15195,7 +15195,7 @@
     <row r="129">
       <c r="A129" s="36" t="inlineStr">
         <is>
-          <t>SRAN10013409</t>
+          <t>SRSR10103462</t>
         </is>
       </c>
       <c r="B129" s="36" t="inlineStr">
@@ -15301,7 +15301,7 @@
     <row r="130">
       <c r="A130" s="29" t="inlineStr">
         <is>
-          <t>PWBG08021221</t>
+          <t>SRBG10025821</t>
         </is>
       </c>
       <c r="B130" s="29" t="inlineStr">
@@ -15411,7 +15411,7 @@
     <row r="131">
       <c r="A131" s="29" t="inlineStr">
         <is>
-          <t>SRSP10091815</t>
+          <t>SRSR10101860</t>
         </is>
       </c>
       <c r="B131" s="29" t="inlineStr">
@@ -15521,7 +15521,7 @@
     <row r="132">
       <c r="A132" s="46" t="inlineStr">
         <is>
-          <t>SRPW10081312</t>
+          <t>SRSR10101358</t>
         </is>
       </c>
       <c r="B132" s="46" t="inlineStr">
@@ -15737,7 +15737,7 @@
     <row r="134">
       <c r="A134" s="46" t="inlineStr">
         <is>
-          <t>PWGB08051204</t>
+          <t>SRGB10055804</t>
         </is>
       </c>
       <c r="B134" s="46" t="inlineStr">
@@ -16161,7 +16161,7 @@
     <row r="138">
       <c r="A138" s="46" t="inlineStr">
         <is>
-          <t>PWSR08101225</t>
+          <t>SRSR10105825</t>
         </is>
       </c>
       <c r="B138" s="46" t="inlineStr">
@@ -16267,7 +16267,7 @@
     <row r="139">
       <c r="A139" s="29" t="inlineStr">
         <is>
-          <t>SRSP10091815</t>
+          <t>SRSR10101860</t>
         </is>
       </c>
       <c r="B139" s="29" t="inlineStr">
@@ -16377,7 +16377,7 @@
     <row r="140">
       <c r="A140" s="29" t="inlineStr">
         <is>
-          <t>SRSP10091815</t>
+          <t>SRSR10101860</t>
         </is>
       </c>
       <c r="B140" s="29" t="inlineStr">
@@ -16593,7 +16593,7 @@
     <row r="142">
       <c r="A142" s="46" t="inlineStr">
         <is>
-          <t>SRAN10013409</t>
+          <t>SRSR10103462</t>
         </is>
       </c>
       <c r="B142" s="46" t="inlineStr">
@@ -17025,7 +17025,7 @@
     <row r="146">
       <c r="A146" s="29" t="inlineStr">
         <is>
-          <t>SRSP10091815</t>
+          <t>SRSR10101860</t>
         </is>
       </c>
       <c r="B146" s="29" t="inlineStr">
@@ -17347,7 +17347,7 @@
     <row r="149">
       <c r="A149" s="29" t="inlineStr">
         <is>
-          <t>SRSP10091815</t>
+          <t>SRSR10101860</t>
         </is>
       </c>
       <c r="B149" s="29" t="inlineStr">
@@ -17457,7 +17457,7 @@
     <row r="150">
       <c r="A150" s="29" t="inlineStr">
         <is>
-          <t>SRSP10091815</t>
+          <t>SRSR10101860</t>
         </is>
       </c>
       <c r="B150" s="29" t="inlineStr">
@@ -17567,7 +17567,7 @@
     <row r="151">
       <c r="A151" s="51" t="inlineStr">
         <is>
-          <t>SRSP10092512</t>
+          <t>SRSR10102559</t>
         </is>
       </c>
       <c r="B151" s="51" t="inlineStr">
@@ -17783,7 +17783,7 @@
     <row r="153">
       <c r="A153" s="29" t="inlineStr">
         <is>
-          <t>SRSP10091815</t>
+          <t>SRSR10101860</t>
         </is>
       </c>
       <c r="B153" s="29" t="inlineStr">
@@ -17893,7 +17893,7 @@
     <row r="154">
       <c r="A154" s="29" t="inlineStr">
         <is>
-          <t>SRSP10091815</t>
+          <t>SRSR10101860</t>
         </is>
       </c>
       <c r="B154" s="29" t="inlineStr">
@@ -18113,7 +18113,7 @@
     <row r="156">
       <c r="A156" s="29" t="inlineStr">
         <is>
-          <t>SRSP10091815</t>
+          <t>SRSR10101860</t>
         </is>
       </c>
       <c r="B156" s="29" t="inlineStr">
@@ -18333,7 +18333,7 @@
     <row r="158">
       <c r="A158" s="29" t="inlineStr">
         <is>
-          <t>SRSP10091815</t>
+          <t>SRSR10101860</t>
         </is>
       </c>
       <c r="B158" s="29" t="inlineStr">
@@ -18443,7 +18443,7 @@
     <row r="159">
       <c r="A159" s="29" t="inlineStr">
         <is>
-          <t>PWSR08101218</t>
+          <t>SRSR10105818</t>
         </is>
       </c>
       <c r="B159" s="29" t="inlineStr">
@@ -18875,7 +18875,7 @@
     <row r="163">
       <c r="A163" s="36" t="inlineStr">
         <is>
-          <t>PWSR08101215</t>
+          <t>SRSR10105815</t>
         </is>
       </c>
       <c r="B163" s="36" t="inlineStr">
@@ -18981,7 +18981,7 @@
     <row r="164">
       <c r="A164" s="46" t="inlineStr">
         <is>
-          <t>PWSR08101225</t>
+          <t>SRSR10105825</t>
         </is>
       </c>
       <c r="B164" s="46" t="inlineStr">
@@ -19193,7 +19193,7 @@
     <row r="166">
       <c r="A166" s="29" t="inlineStr">
         <is>
-          <t>SRSP10091815</t>
+          <t>SRSR10101860</t>
         </is>
       </c>
       <c r="B166" s="29" t="inlineStr">
@@ -19303,7 +19303,7 @@
     <row r="167">
       <c r="A167" s="29" t="inlineStr">
         <is>
-          <t>SRSP10091815</t>
+          <t>SRSR10101860</t>
         </is>
       </c>
       <c r="B167" s="29" t="inlineStr">
@@ -19413,7 +19413,7 @@
     <row r="168">
       <c r="A168" s="46" t="inlineStr">
         <is>
-          <t>PWSR08101225</t>
+          <t>SRSR10105825</t>
         </is>
       </c>
       <c r="B168" s="46" t="inlineStr">
@@ -19629,7 +19629,7 @@
     <row r="170">
       <c r="A170" s="29" t="inlineStr">
         <is>
-          <t>PWSP08091416</t>
+          <t>SRSR10105866</t>
         </is>
       </c>
       <c r="B170" s="29" t="inlineStr">
@@ -19845,7 +19845,7 @@
     <row r="172">
       <c r="A172" s="55" t="inlineStr">
         <is>
-          <t>SRSP10092512</t>
+          <t>SRSR10102559</t>
         </is>
       </c>
       <c r="B172" s="55" t="inlineStr">
@@ -20057,7 +20057,7 @@
     <row r="174">
       <c r="A174" s="46" t="inlineStr">
         <is>
-          <t>PWSR08101208</t>
+          <t>SRSR10105808</t>
         </is>
       </c>
       <c r="B174" s="46" t="inlineStr">
@@ -20273,7 +20273,7 @@
     <row r="176">
       <c r="A176" s="29" t="inlineStr">
         <is>
-          <t>PWBG08021221</t>
+          <t>SRBG10025821</t>
         </is>
       </c>
       <c r="B176" s="29" t="inlineStr">
@@ -20383,7 +20383,7 @@
     <row r="177">
       <c r="A177" s="36" t="inlineStr">
         <is>
-          <t>BGPW02082212</t>
+          <t>BGSR02102258</t>
         </is>
       </c>
       <c r="B177" s="36" t="inlineStr">
@@ -20489,7 +20489,7 @@
     <row r="178">
       <c r="A178" s="46" t="inlineStr">
         <is>
-          <t>BGPW02082212</t>
+          <t>BGSR02102258</t>
         </is>
       </c>
       <c r="B178" s="46" t="inlineStr">
@@ -20595,7 +20595,7 @@
     <row r="179">
       <c r="A179" s="29" t="inlineStr">
         <is>
-          <t>SRSP10091815</t>
+          <t>SRSR10101860</t>
         </is>
       </c>
       <c r="B179" s="29" t="inlineStr">
@@ -20705,7 +20705,7 @@
     <row r="180">
       <c r="A180" s="29" t="inlineStr">
         <is>
-          <t>SRSP10091815</t>
+          <t>SRSR10101860</t>
         </is>
       </c>
       <c r="B180" s="29" t="inlineStr">
@@ -20921,7 +20921,7 @@
     <row r="182">
       <c r="A182" s="29" t="inlineStr">
         <is>
-          <t>SRSP10091815</t>
+          <t>SRSR10101860</t>
         </is>
       </c>
       <c r="B182" s="29" t="inlineStr">
@@ -21349,7 +21349,7 @@
     <row r="186">
       <c r="A186" s="46" t="inlineStr">
         <is>
-          <t>BGPW02082212</t>
+          <t>BGSR02102258</t>
         </is>
       </c>
       <c r="B186" s="46" t="inlineStr">
@@ -21561,7 +21561,7 @@
     <row r="188">
       <c r="A188" s="46" t="inlineStr">
         <is>
-          <t>PWSR08101225</t>
+          <t>SRSR10105825</t>
         </is>
       </c>
       <c r="B188" s="46" t="inlineStr">
@@ -21667,7 +21667,7 @@
     <row r="189">
       <c r="A189" s="29" t="inlineStr">
         <is>
-          <t>SRSP10091815</t>
+          <t>SRSR10101860</t>
         </is>
       </c>
       <c r="B189" s="29" t="inlineStr">
@@ -21777,7 +21777,7 @@
     <row r="190">
       <c r="A190" s="46" t="inlineStr">
         <is>
-          <t>SRAN10013409</t>
+          <t>SRSR10103462</t>
         </is>
       </c>
       <c r="B190" s="46" t="inlineStr">
@@ -22099,7 +22099,7 @@
     <row r="193">
       <c r="A193" s="36" t="inlineStr">
         <is>
-          <t>PWSR08101225</t>
+          <t>SRSR10105825</t>
         </is>
       </c>
       <c r="B193" s="36" t="inlineStr">
@@ -22205,7 +22205,7 @@
     <row r="194">
       <c r="A194" s="46" t="inlineStr">
         <is>
-          <t>SRAN10013409</t>
+          <t>SRSR10103462</t>
         </is>
       </c>
       <c r="B194" s="46" t="inlineStr">
@@ -22527,7 +22527,7 @@
     <row r="197">
       <c r="A197" s="36" t="inlineStr">
         <is>
-          <t>PWSR08101225</t>
+          <t>SRSR10105825</t>
         </is>
       </c>
       <c r="B197" s="36" t="inlineStr">
@@ -22633,7 +22633,7 @@
     <row r="198">
       <c r="A198" s="46" t="inlineStr">
         <is>
-          <t>PWSR08101225</t>
+          <t>SRSR10105825</t>
         </is>
       </c>
       <c r="B198" s="46" t="inlineStr">
@@ -22739,7 +22739,7 @@
     <row r="199">
       <c r="A199" s="29" t="inlineStr">
         <is>
-          <t>SRSP10091815</t>
+          <t>SRSR10101860</t>
         </is>
       </c>
       <c r="B199" s="29" t="inlineStr">
@@ -22955,7 +22955,7 @@
     <row r="201">
       <c r="A201" s="29" t="inlineStr">
         <is>
-          <t>SRSP10091815</t>
+          <t>SRSR10101860</t>
         </is>
       </c>
       <c r="B201" s="29" t="inlineStr">
@@ -23065,7 +23065,7 @@
     <row r="202">
       <c r="A202" s="29" t="inlineStr">
         <is>
-          <t>SRSP10091815</t>
+          <t>SRSR10101860</t>
         </is>
       </c>
       <c r="B202" s="29" t="inlineStr">
@@ -23175,7 +23175,7 @@
     <row r="203">
       <c r="A203" s="29" t="inlineStr">
         <is>
-          <t>PWBG08021221</t>
+          <t>SRBG10025821</t>
         </is>
       </c>
       <c r="B203" s="29" t="inlineStr">
@@ -23285,7 +23285,7 @@
     <row r="204">
       <c r="A204" s="46" t="inlineStr">
         <is>
-          <t>PWSR08101225</t>
+          <t>SRSR10105825</t>
         </is>
       </c>
       <c r="B204" s="46" t="inlineStr">
@@ -23603,7 +23603,7 @@
     <row r="207">
       <c r="A207" s="29" t="inlineStr">
         <is>
-          <t>SRSP10091815</t>
+          <t>SRSR10101860</t>
         </is>
       </c>
       <c r="B207" s="29" t="inlineStr">
@@ -23933,7 +23933,7 @@
     <row r="210">
       <c r="A210" s="42" t="inlineStr">
         <is>
-          <t>BGAN02012209</t>
+          <t>BGSR02102262</t>
         </is>
       </c>
       <c r="B210" s="42" t="inlineStr">
@@ -24043,7 +24043,7 @@
     <row r="211">
       <c r="A211" s="42" t="inlineStr">
         <is>
-          <t>BGAN02012209</t>
+          <t>BGSR02102262</t>
         </is>
       </c>
       <c r="B211" s="42" t="inlineStr">
@@ -24153,7 +24153,7 @@
     <row r="212">
       <c r="A212" s="42" t="inlineStr">
         <is>
-          <t>BGAN02012209</t>
+          <t>BGSR02102262</t>
         </is>
       </c>
       <c r="B212" s="42" t="inlineStr">
@@ -24373,7 +24373,7 @@
     <row r="214">
       <c r="A214" s="46" t="inlineStr">
         <is>
-          <t>PWSR08101225</t>
+          <t>SRSR10105825</t>
         </is>
       </c>
       <c r="B214" s="46" t="inlineStr">
@@ -24479,7 +24479,7 @@
     <row r="215">
       <c r="A215" s="36" t="inlineStr">
         <is>
-          <t>KWSP07090815</t>
+          <t>SRSR10106360</t>
         </is>
       </c>
       <c r="B215" s="36" t="inlineStr">
@@ -24585,7 +24585,7 @@
     <row r="216">
       <c r="A216" s="29" t="inlineStr">
         <is>
-          <t>SRSP10091815</t>
+          <t>SRSR10101860</t>
         </is>
       </c>
       <c r="B216" s="29" t="inlineStr">
@@ -24911,7 +24911,7 @@
     <row r="219">
       <c r="A219" s="42" t="inlineStr">
         <is>
-          <t>BGAN02012209</t>
+          <t>BGSR02102262</t>
         </is>
       </c>
       <c r="B219" s="42" t="inlineStr">
@@ -25021,7 +25021,7 @@
     <row r="220">
       <c r="A220" s="42" t="inlineStr">
         <is>
-          <t>BGAN02012209</t>
+          <t>BGSR02102262</t>
         </is>
       </c>
       <c r="B220" s="42" t="inlineStr">
@@ -25131,7 +25131,7 @@
     <row r="221">
       <c r="A221" s="36" t="inlineStr">
         <is>
-          <t>PWSR08101225</t>
+          <t>SRSR10105825</t>
         </is>
       </c>
       <c r="B221" s="36" t="inlineStr">
@@ -25237,7 +25237,7 @@
     <row r="222">
       <c r="A222" s="29" t="inlineStr">
         <is>
-          <t>SRSP10091815</t>
+          <t>SRSR10101860</t>
         </is>
       </c>
       <c r="B222" s="29" t="inlineStr">
@@ -25347,7 +25347,7 @@
     <row r="223">
       <c r="A223" s="36" t="inlineStr">
         <is>
-          <t>SRSP10093415</t>
+          <t>SRSR10103460</t>
         </is>
       </c>
       <c r="B223" s="36" t="inlineStr">
@@ -25559,7 +25559,7 @@
     <row r="225">
       <c r="A225" s="36" t="inlineStr">
         <is>
-          <t>SRSP10093415</t>
+          <t>SRSR10103460</t>
         </is>
       </c>
       <c r="B225" s="36" t="inlineStr">
@@ -25665,7 +25665,7 @@
     <row r="226">
       <c r="A226" s="29" t="inlineStr">
         <is>
-          <t>SRSP10091815</t>
+          <t>SRSR10101860</t>
         </is>
       </c>
       <c r="B226" s="29" t="inlineStr">
@@ -25775,7 +25775,7 @@
     <row r="227">
       <c r="A227" s="29" t="inlineStr">
         <is>
-          <t>SRSP10091815</t>
+          <t>SRSR10101860</t>
         </is>
       </c>
       <c r="B227" s="29" t="inlineStr">
@@ -25885,7 +25885,7 @@
     <row r="228">
       <c r="A228" s="29" t="inlineStr">
         <is>
-          <t>SRSP10091815</t>
+          <t>SRSR10101860</t>
         </is>
       </c>
       <c r="B228" s="29" t="inlineStr">
@@ -25995,7 +25995,7 @@
     <row r="229">
       <c r="A229" s="29" t="inlineStr">
         <is>
-          <t>SRSP10091815</t>
+          <t>SRSR10101860</t>
         </is>
       </c>
       <c r="B229" s="29" t="inlineStr">
@@ -26105,7 +26105,7 @@
     <row r="230">
       <c r="A230" s="46" t="inlineStr">
         <is>
-          <t>PWAN08011213</t>
+          <t>SRAN10015813</t>
         </is>
       </c>
       <c r="B230" s="46" t="inlineStr">
@@ -26211,7 +26211,7 @@
     <row r="231">
       <c r="A231" s="36" t="inlineStr">
         <is>
-          <t>PWSR08101225</t>
+          <t>SRSR10105825</t>
         </is>
       </c>
       <c r="B231" s="36" t="inlineStr">
@@ -26317,7 +26317,7 @@
     <row r="232">
       <c r="A232" s="46" t="inlineStr">
         <is>
-          <t>PWSR08101225</t>
+          <t>SRSR10105825</t>
         </is>
       </c>
       <c r="B232" s="46" t="inlineStr">
@@ -26529,7 +26529,7 @@
     <row r="234">
       <c r="A234" s="46" t="inlineStr">
         <is>
-          <t>SRAN10013409</t>
+          <t>SRSR10103462</t>
         </is>
       </c>
       <c r="B234" s="46" t="inlineStr">
@@ -26635,7 +26635,7 @@
     <row r="235">
       <c r="A235" s="29" t="inlineStr">
         <is>
-          <t>SRSP10091815</t>
+          <t>SRSR10101860</t>
         </is>
       </c>
       <c r="B235" s="29" t="inlineStr">
@@ -26745,7 +26745,7 @@
     <row r="236">
       <c r="A236" s="46" t="inlineStr">
         <is>
-          <t>PWSR08101225</t>
+          <t>SRSR10105825</t>
         </is>
       </c>
       <c r="B236" s="46" t="inlineStr">
@@ -26851,7 +26851,7 @@
     <row r="237">
       <c r="A237" s="29" t="inlineStr">
         <is>
-          <t>PWSP08091215</t>
+          <t>SRSR10105860</t>
         </is>
       </c>
       <c r="B237" s="29" t="inlineStr">
@@ -26961,7 +26961,7 @@
     <row r="238">
       <c r="A238" s="29" t="inlineStr">
         <is>
-          <t>PWSR08101218</t>
+          <t>SRSR10105818</t>
         </is>
       </c>
       <c r="B238" s="29" t="inlineStr">
@@ -27071,7 +27071,7 @@
     <row r="239">
       <c r="A239" s="29" t="inlineStr">
         <is>
-          <t>PWSR08101218</t>
+          <t>SRSR10105818</t>
         </is>
       </c>
       <c r="B239" s="29" t="inlineStr">
@@ -27181,7 +27181,7 @@
     <row r="240">
       <c r="A240" s="46" t="inlineStr">
         <is>
-          <t>PWAN08011213</t>
+          <t>SRAN10015813</t>
         </is>
       </c>
       <c r="B240" s="46" t="inlineStr">
@@ -27287,7 +27287,7 @@
     <row r="241">
       <c r="A241" s="29" t="inlineStr">
         <is>
-          <t>PWSP08091215</t>
+          <t>SRSR10105860</t>
         </is>
       </c>
       <c r="B241" s="29" t="inlineStr">
@@ -27397,7 +27397,7 @@
     <row r="242">
       <c r="A242" s="29" t="inlineStr">
         <is>
-          <t>SRSP10091815</t>
+          <t>SRSR10101860</t>
         </is>
       </c>
       <c r="B242" s="29" t="inlineStr">
@@ -27507,7 +27507,7 @@
     <row r="243">
       <c r="A243" s="29" t="inlineStr">
         <is>
-          <t>PWSP08091215</t>
+          <t>SRSR10105860</t>
         </is>
       </c>
       <c r="B243" s="29" t="inlineStr">
@@ -27617,7 +27617,7 @@
     <row r="244">
       <c r="A244" s="29" t="inlineStr">
         <is>
-          <t>PWSR08101218</t>
+          <t>SRSR10105818</t>
         </is>
       </c>
       <c r="B244" s="29" t="inlineStr">
@@ -27727,7 +27727,7 @@
     <row r="245">
       <c r="A245" s="36" t="inlineStr">
         <is>
-          <t>BRKW04070207</t>
+          <t>SRSR10106444</t>
         </is>
       </c>
       <c r="B245" s="36" t="inlineStr">
@@ -27833,7 +27833,7 @@
     <row r="246">
       <c r="A246" s="29" t="inlineStr">
         <is>
-          <t>PWSP08091215</t>
+          <t>SRSR10105860</t>
         </is>
       </c>
       <c r="B246" s="29" t="inlineStr">
@@ -27943,7 +27943,7 @@
     <row r="247">
       <c r="A247" s="29" t="inlineStr">
         <is>
-          <t>PWSP08091215</t>
+          <t>SRSR10105860</t>
         </is>
       </c>
       <c r="B247" s="29" t="inlineStr">
@@ -28053,7 +28053,7 @@
     <row r="248">
       <c r="A248" s="29" t="inlineStr">
         <is>
-          <t>BRAN04010109</t>
+          <t>BRSR04100162</t>
         </is>
       </c>
       <c r="B248" s="29" t="inlineStr">
@@ -28163,7 +28163,7 @@
     <row r="249">
       <c r="A249" s="36" t="inlineStr">
         <is>
-          <t>SRPW10081312</t>
+          <t>SRSR10101358</t>
         </is>
       </c>
       <c r="B249" s="36" t="inlineStr">
@@ -28269,7 +28269,7 @@
     <row r="250">
       <c r="A250" s="29" t="inlineStr">
         <is>
-          <t>PWSP08091215</t>
+          <t>SRSR10105860</t>
         </is>
       </c>
       <c r="B250" s="29" t="inlineStr">
@@ -28379,7 +28379,7 @@
     <row r="251">
       <c r="A251" s="29" t="inlineStr">
         <is>
-          <t>PWSP08091215</t>
+          <t>SRSR10105860</t>
         </is>
       </c>
       <c r="B251" s="29" t="inlineStr">
@@ -28489,7 +28489,7 @@
     <row r="252">
       <c r="A252" s="46" t="inlineStr">
         <is>
-          <t>PWSR08101225</t>
+          <t>SRSR10105825</t>
         </is>
       </c>
       <c r="B252" s="46" t="inlineStr">
@@ -28595,7 +28595,7 @@
     <row r="253">
       <c r="A253" s="29" t="inlineStr">
         <is>
-          <t>PWSP08091215</t>
+          <t>SRSR10105860</t>
         </is>
       </c>
       <c r="B253" s="29" t="inlineStr">
@@ -28705,7 +28705,7 @@
     <row r="254">
       <c r="A254" s="29" t="inlineStr">
         <is>
-          <t>BRAN04010109</t>
+          <t>BRSR04100162</t>
         </is>
       </c>
       <c r="B254" s="29" t="inlineStr">
@@ -28815,7 +28815,7 @@
     <row r="255">
       <c r="A255" s="29" t="inlineStr">
         <is>
-          <t>PWAN08011209</t>
+          <t>SRSR10105862</t>
         </is>
       </c>
       <c r="B255" s="29" t="inlineStr">
@@ -28925,7 +28925,7 @@
     <row r="256">
       <c r="A256" s="29" t="inlineStr">
         <is>
-          <t>SRSP10091815</t>
+          <t>SRSR10101860</t>
         </is>
       </c>
       <c r="B256" s="29" t="inlineStr">
@@ -29035,7 +29035,7 @@
     <row r="257">
       <c r="A257" s="29" t="inlineStr">
         <is>
-          <t>BRAN04010109</t>
+          <t>BRSR04100162</t>
         </is>
       </c>
       <c r="B257" s="29" t="inlineStr">
@@ -29145,7 +29145,7 @@
     <row r="258">
       <c r="A258" s="29" t="inlineStr">
         <is>
-          <t>PWAN08011209</t>
+          <t>SRSR10105862</t>
         </is>
       </c>
       <c r="B258" s="29" t="inlineStr">
@@ -29365,7 +29365,7 @@
     <row r="260">
       <c r="A260" s="29" t="inlineStr">
         <is>
-          <t>PWSP08091215</t>
+          <t>SRSR10105860</t>
         </is>
       </c>
       <c r="B260" s="29" t="inlineStr">
@@ -29475,7 +29475,7 @@
     <row r="261">
       <c r="A261" s="36" t="inlineStr">
         <is>
-          <t>PWGB08051204</t>
+          <t>SRGB10055804</t>
         </is>
       </c>
       <c r="B261" s="36" t="inlineStr">
@@ -29581,7 +29581,7 @@
     <row r="262">
       <c r="A262" s="46" t="inlineStr">
         <is>
-          <t>PWGB08051204</t>
+          <t>SRGB10055804</t>
         </is>
       </c>
       <c r="B262" s="46" t="inlineStr">
@@ -29687,7 +29687,7 @@
     <row r="263">
       <c r="A263" s="29" t="inlineStr">
         <is>
-          <t>PWSR08101218</t>
+          <t>SRSR10105818</t>
         </is>
       </c>
       <c r="B263" s="29" t="inlineStr">
@@ -29903,7 +29903,7 @@
     <row r="265">
       <c r="A265" s="36" t="inlineStr">
         <is>
-          <t>KWSP07090815</t>
+          <t>SRSR10106360</t>
         </is>
       </c>
       <c r="B265" s="36" t="inlineStr">
@@ -30009,7 +30009,7 @@
     <row r="266">
       <c r="A266" s="55" t="inlineStr">
         <is>
-          <t>SRSP10092512</t>
+          <t>SRSR10102559</t>
         </is>
       </c>
       <c r="B266" s="55" t="inlineStr">
@@ -30115,7 +30115,7 @@
     <row r="267">
       <c r="A267" s="36" t="inlineStr">
         <is>
-          <t>BRKW04070207</t>
+          <t>SRBG10026421</t>
         </is>
       </c>
       <c r="B267" s="36" t="inlineStr">
@@ -30433,7 +30433,7 @@
     <row r="270">
       <c r="A270" s="29" t="inlineStr">
         <is>
-          <t>PWSR08101218</t>
+          <t>SRSR10105818</t>
         </is>
       </c>
       <c r="B270" s="29" t="inlineStr">
@@ -30543,7 +30543,7 @@
     <row r="271">
       <c r="A271" s="29" t="inlineStr">
         <is>
-          <t>PWSR08101218</t>
+          <t>SRSR10105818</t>
         </is>
       </c>
       <c r="B271" s="29" t="inlineStr">
@@ -30653,7 +30653,7 @@
     <row r="272">
       <c r="A272" s="29" t="inlineStr">
         <is>
-          <t>PWSR08101218</t>
+          <t>SRSR10105818</t>
         </is>
       </c>
       <c r="B272" s="29" t="inlineStr">
@@ -30763,7 +30763,7 @@
     <row r="273">
       <c r="A273" s="29" t="inlineStr">
         <is>
-          <t>PWSP08091215</t>
+          <t>SRSR10105860</t>
         </is>
       </c>
       <c r="B273" s="29" t="inlineStr">
@@ -30873,7 +30873,7 @@
     <row r="274">
       <c r="A274" s="29" t="inlineStr">
         <is>
-          <t>PWSP08091215</t>
+          <t>SRSR10105860</t>
         </is>
       </c>
       <c r="B274" s="29" t="inlineStr">
@@ -31199,7 +31199,7 @@
     <row r="277">
       <c r="A277" s="29" t="inlineStr">
         <is>
-          <t>PWSP08091215</t>
+          <t>SRSR10105860</t>
         </is>
       </c>
       <c r="B277" s="29" t="inlineStr">
@@ -31309,7 +31309,7 @@
     <row r="278">
       <c r="A278" s="55" t="inlineStr">
         <is>
-          <t>SRSP10092512</t>
+          <t>SRSR10102559</t>
         </is>
       </c>
       <c r="B278" s="55" t="inlineStr">
@@ -31415,7 +31415,7 @@
     <row r="279">
       <c r="A279" s="29" t="inlineStr">
         <is>
-          <t>PWSP08091215</t>
+          <t>SRSR10105860</t>
         </is>
       </c>
       <c r="B279" s="29" t="inlineStr">
@@ -31525,7 +31525,7 @@
     <row r="280">
       <c r="A280" s="29" t="inlineStr">
         <is>
-          <t>PWSP08091215</t>
+          <t>SRSR10105860</t>
         </is>
       </c>
       <c r="B280" s="29" t="inlineStr">
@@ -35565,7 +35565,7 @@
     <row r="318">
       <c r="A318" s="55" t="inlineStr">
         <is>
-          <t>SPSR09101539</t>
+          <t>SRSR10106039</t>
         </is>
       </c>
       <c r="B318" s="55" t="inlineStr">
@@ -45437,7 +45437,7 @@
       </c>
       <c r="C5" s="75" t="inlineStr">
         <is>
-          <t>30 May 2026</t>
+          <t>03 Jun 2026</t>
         </is>
       </c>
     </row>
